--- a/naver-place-crawler/results_derma/분당_피부과.xlsx
+++ b/naver-place-crawler/results_derma/분당_피부과.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,30 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>분당 맥스웰의원</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>박병찬피부과의원</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>et941104@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-717-5824</t>
+          <t>031-719-5500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 7 301호</t>
+          <t>경기도 성남시 분당구 내정로165번길 50 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://bundang.maxwellhair.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -613,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1494157050</t>
+          <t>13234870</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494157050</t>
+          <t>https://m.place.naver.com/place/13234870</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -654,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>로즈피부과 분당점</t>
+          <t>분당프리미어의원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>roseclinic_@naver.com</t>
+          <t>isigary@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1437-9970</t>
+          <t>0507-1405-7918</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 27 하나프라자 6층</t>
+          <t>경기도 성남시 분당구 백현로101번길 29 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.roseclinic.kr/</t>
+          <t>https://blog.naver.com/isigary</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>130</v>
+        <v>613</v>
       </c>
       <c r="Q3" t="n">
-        <v>290</v>
+        <v>3994</v>
       </c>
       <c r="R3" t="n">
-        <v>420</v>
+        <v>4607</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>12952311</t>
+          <t>1095182275</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12952311</t>
+          <t>https://m.place.naver.com/place/1095182275</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -748,44 +752,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성맑은피부과의원</t>
+          <t>오브디의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sspureclinic@naver.com</t>
+          <t>dr_kkang@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-698-4016</t>
+          <t>0507-1383-5702</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 4층</t>
+          <t>경기도 성남시 분당구 느티로 16 젤존타워1 5층 510호 오브디의원</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://sspureclinic.com</t>
+          <t>https://blog.naver.com/dr_kkang</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -796,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>447</v>
+        <v>292</v>
       </c>
       <c r="Q4" t="n">
-        <v>203</v>
+        <v>2774</v>
       </c>
       <c r="R4" t="n">
-        <v>650</v>
+        <v>3066</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1582994500</t>
+          <t>1260816786</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1582994500</t>
+          <t>https://m.place.naver.com/place/1260816786</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -842,44 +846,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>분당동안의원</t>
+          <t>오늘맑음의원 분당</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pix1246@naver.com</t>
+          <t>familiar8622@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-708-0822</t>
+          <t>031-709-7202</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 35 현대프라자 4층 407호</t>
+          <t>경기도 성남시 분당구 서현로210번길 2 5층 501호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.donganclinicbd.com/</t>
+          <t>https://www.instagram.com/clear_today1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="Q5" t="n">
-        <v>1881</v>
+        <v>3941</v>
       </c>
       <c r="R5" t="n">
-        <v>2390</v>
+        <v>4476</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>12943172</t>
+          <t>1014948722</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12943172</t>
+          <t>https://m.place.naver.com/place/1014948722</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -936,39 +940,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>메이린의원 판교</t>
+          <t>밴스의원 판교역</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pangyomaylin@naver.com</t>
+          <t>lcevsly@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1301-3246</t>
+          <t>031-8039-7570</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 10층 메이린클리닉 판교점</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠판교 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maylinclinic_pg/</t>
+          <t>https://pangyo.vandsclinic.co.kr/?channel=4155</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -984,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>117</v>
+        <v>1868</v>
       </c>
       <c r="Q6" t="n">
-        <v>147</v>
+        <v>702</v>
       </c>
       <c r="R6" t="n">
-        <v>264</v>
+        <v>2570</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37035893</t>
+          <t>1947822332</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37035893</t>
+          <t>https://m.place.naver.com/place/1947822332</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오월의아침피부과의원</t>
+          <t>소호의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>maymorning_05@naver.com</t>
+          <t>mbzoo91@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-717-5207</t>
+          <t>031-702-5060</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 46 광천프라자 5층 오월의아침피부과의원</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 30 소호클리닉</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.maymorning.kr/</t>
+          <t>http://sohoclinic.co.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,22 +1082,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>501</v>
+        <v>330</v>
       </c>
       <c r="Q7" t="n">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
-        <v>619</v>
+        <v>351</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>12771235</t>
+          <t>1935241872</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12771235</t>
+          <t>https://m.place.naver.com/place/1935241872</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1124,39 +1128,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>소호의원</t>
+          <t>미소앤의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mbzoo91@naver.com</t>
+          <t>misoenclinic@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-702-5060</t>
+          <t>0507-1495-7478</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 30 소호클리닉</t>
+          <t>경기도 성남시 분당구 성남대로 168 미도프라자 6층 601호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://sohoclinic.co.kr</t>
+          <t>https://blog.naver.com/misoenclinic</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>329</v>
+        <v>156</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="R8" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1935241872</t>
+          <t>1467523840</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935241872</t>
+          <t>https://m.place.naver.com/place/1467523840</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1218,30 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>메이퓨어의원 야탑점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>블리비의원 분당점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sungjaelwwhyu@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-399-9990</t>
+          <t>1833-3130</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 6층 608호</t>
+          <t>경기도 성남시 분당구 서현로210번길 2 성지하이츠텔 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>https://www.velyb.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1262,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2452</v>
+        <v>1341</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>2544</v>
       </c>
       <c r="R9" t="n">
-        <v>2476</v>
+        <v>3885</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36654949</t>
+          <t>2076023323</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36654949</t>
+          <t>https://m.place.naver.com/place/2076023323</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>수내메이퓨어의원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>닥터스피부과의원 서판교</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>doctorspg@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-717-3336</t>
+          <t>031-698-3088</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 97 수내동 다운타운 1004호</t>
+          <t>경기도 성남시 분당구 운중로 237 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>http://seopangyo.doctors365.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1336,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1357,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1046</v>
+        <v>319</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="R10" t="n">
-        <v>1079</v>
+        <v>409</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1638817358</t>
+          <t>1937925934</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1638817358</t>
+          <t>https://m.place.naver.com/place/1937925934</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1398,33 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리더스피부과의원 판교</t>
+          <t>다시봄날의원 분당</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leaderspgd@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>master@beautyleader.co.kr</t>
-        </is>
-      </c>
+          <t>yesokkim0510@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-8023-5085</t>
+          <t>0507-1488-7676</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 판교리더스피부과</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 제5층 501-2호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://leaders-pg.com/</t>
+          <t>https://bd.springdayclinic.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>421</v>
+        <v>932</v>
       </c>
       <c r="Q11" t="n">
-        <v>1460</v>
+        <v>5248</v>
       </c>
       <c r="R11" t="n">
-        <v>1881</v>
+        <v>6180</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>21697693</t>
+          <t>1986908099</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21697693</t>
+          <t>https://m.place.naver.com/place/1986908099</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1496,25 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>밴스의원 판교역</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>포레스트의원</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>forest_derma@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-8039-7570</t>
+          <t>0507-1343-3890</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠판교 3층</t>
+          <t>경기도 성남시 분당구 황새울로335번길 5 N타운빌딩 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://pangyo.vandsclinic.co.kr/?channel=4155</t>
+          <t>https://forest.quv.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1529,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1545,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1855</v>
+        <v>593</v>
       </c>
       <c r="Q12" t="n">
-        <v>701</v>
+        <v>6306</v>
       </c>
       <c r="R12" t="n">
-        <v>2556</v>
+        <v>6899</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1947822332</t>
+          <t>32430482</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1947822332</t>
+          <t>https://m.place.naver.com/place/32430482</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1586,34 +1598,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>새로운봄의원</t>
+          <t>노블클래식의원 분당</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ryu3wishesps@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>miosol@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>team@madeinreal.com</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>031-701-0880</t>
+          <t>031-707-7930</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 마크시티그린빌딩 403호</t>
+          <t>경기도 성남시 분당구 성남대로926번길 6 대덕프라자 407호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ryu3wishesps</t>
+          <t>https://www.noblebundang.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1639,17 +1655,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>353</v>
+        <v>491</v>
       </c>
       <c r="Q13" t="n">
-        <v>890</v>
+        <v>957</v>
       </c>
       <c r="R13" t="n">
-        <v>1243</v>
+        <v>1448</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1674,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1833192483</t>
+          <t>35701207</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1833192483</t>
+          <t>https://m.place.naver.com/place/35701207</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1680,43 +1696,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>노블클래식의원 분당</t>
+          <t>이지함피부과의원 분당점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>miosol@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>team@madeinreal.com</t>
-        </is>
-      </c>
+          <t>bundangleejiham@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>031-707-7930</t>
+          <t>0507-1440-2105</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 6 대덕프라자 407호</t>
+          <t>경기도 성남시 분당구 서현로 204 엘지분당에클라트2차 402, 403호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.noblebundang.com/</t>
+          <t>https://blog.naver.com/bundangleejiham</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1737,17 +1749,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>491</v>
+        <v>228</v>
       </c>
       <c r="Q14" t="n">
-        <v>1004</v>
+        <v>383</v>
       </c>
       <c r="R14" t="n">
-        <v>1495</v>
+        <v>611</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1768,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>35701207</t>
+          <t>13234600</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35701207</t>
+          <t>https://m.place.naver.com/place/13234600</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1790,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>분당 톡스앤필의원</t>
+          <t>예라인의원 분당</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>toxnfill5@naver.com</t>
+          <t>planet46635@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>031-707-3500</t>
+          <t>031-703-4400</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로343번길 12-2 5층</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 506호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.toxnfill5.com</t>
+          <t>https://blog.naver.com/planet46635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1835,13 +1847,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>822</v>
+        <v>145</v>
       </c>
       <c r="Q15" t="n">
-        <v>5591</v>
+        <v>6717</v>
       </c>
       <c r="R15" t="n">
-        <v>6413</v>
+        <v>6862</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1862,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1299969468</t>
+          <t>1343652932</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299969468</t>
+          <t>https://m.place.naver.com/place/1343652932</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1941,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q16" t="n">
-        <v>1483</v>
+        <v>1512</v>
       </c>
       <c r="R16" t="n">
-        <v>1688</v>
+        <v>1718</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1966,30 +1978,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>연세모네피부과의원</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>포에버의원 분당</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4everbun@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>031-709-6354</t>
+          <t>0507-1365-8348</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 22 블루홀플라자</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://bd.4-ever.co.kr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1999,7 +2015,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2010,22 +2026,22 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>224</v>
+        <v>982</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>2907</v>
       </c>
       <c r="R17" t="n">
-        <v>234</v>
+        <v>3889</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2050,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>11538782</t>
+          <t>20747205</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11538782</t>
+          <t>https://m.place.naver.com/place/20747205</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2072,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>오늘맑음의원 분당</t>
+          <t>아비쥬의원 분당</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>familiar8622@naver.com</t>
+          <t>hj_4326@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>031-709-7202</t>
+          <t>031-607-1717</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 2 5층 501호</t>
+          <t>경기도 성남시 분당구 분당로53번길 10 동호프라자 401호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/clear_today1</t>
+          <t>https://blog.naver.com/hj_4326</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2093,7 +2109,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2104,7 +2120,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2113,13 +2129,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>534</v>
+        <v>2129</v>
       </c>
       <c r="Q18" t="n">
-        <v>3946</v>
+        <v>277</v>
       </c>
       <c r="R18" t="n">
-        <v>4480</v>
+        <v>2406</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2144,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1014948722</t>
+          <t>1202847355</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1014948722</t>
+          <t>https://m.place.naver.com/place/1202847355</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2150,44 +2166,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>예라인의원 분당</t>
+          <t>루이의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>planet46635@naver.com</t>
+          <t>louisclinic-4008@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>031-703-4400</t>
+          <t>0507-1398-4009</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 506호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 3층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/planet46635</t>
+          <t>http://louisclinic.com/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2207,13 +2223,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>145</v>
+        <v>405</v>
       </c>
       <c r="Q19" t="n">
-        <v>6505</v>
+        <v>2429</v>
       </c>
       <c r="R19" t="n">
-        <v>6650</v>
+        <v>2834</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2238,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1343652932</t>
+          <t>36428162</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1343652932</t>
+          <t>https://m.place.naver.com/place/36428162</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2260,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>유어라인의원</t>
+          <t>미금동안마녀의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yourlineclinic@naver.com</t>
+          <t>mintcavatina@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>031-715-3657</t>
+          <t>0507-1379-4725</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 73 우방코아 5층 503호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 2층 206호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xfxexdxhn</t>
+          <t>http://www.witchclinic.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2276,12 +2292,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2301,13 +2317,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>198</v>
+        <v>491</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="R20" t="n">
-        <v>230</v>
+        <v>736</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2332,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1898979899</t>
+          <t>1301944577</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1898979899</t>
+          <t>https://m.place.naver.com/place/1301944577</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2354,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>해피닥터의원 분당</t>
+          <t>티앤티의원</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>breathe5307@naver.com</t>
+          <t>fatrasue@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>031-704-0008</t>
+          <t>031-608-0085</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 227 백궁지엔느빌딩</t>
+          <t>경기도 성남시 분당구 분당로53번길 12 5층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.happydoctor.co.kr</t>
+          <t>http://tntclinic.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2395,13 +2411,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>783</v>
+        <v>1465</v>
       </c>
       <c r="Q21" t="n">
-        <v>1452</v>
+        <v>3002</v>
       </c>
       <c r="R21" t="n">
-        <v>2235</v>
+        <v>4467</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2426,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12851894</t>
+          <t>1778414883</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12851894</t>
+          <t>https://m.place.naver.com/place/1778414883</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2448,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아젤린의원 정자</t>
+          <t>뷰티라운지의원 판교점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>azelin-bundang@naver.com</t>
+          <t>beautyloungeclinic@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1383-1745</t>
+          <t>031-698-3727</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존타워3 3층 306호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움타워 2동 지하1층 뷰티라운지의원</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://www.azelin.co.kr/</t>
+          <t>http://pangyo.beautyloungeclinic.com/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2469,7 +2485,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2489,13 +2505,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>835</v>
+        <v>549</v>
       </c>
       <c r="Q22" t="n">
-        <v>823</v>
+        <v>2293</v>
       </c>
       <c r="R22" t="n">
-        <v>1658</v>
+        <v>2842</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2520,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37745081</t>
+          <t>1742515435</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37745081</t>
+          <t>https://m.place.naver.com/place/1742515435</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2526,34 +2542,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>미금밴스의원</t>
+          <t>아이로피부과의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>yeobuja_@naver.com</t>
+          <t>fogunion@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>031-778-8037</t>
+          <t>031-8016-1675</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 86 엘레강스프라자B동 8층 801호</t>
+          <t>경기도 성남시 분당구 운중로 142 401호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://migeum.vandsclinic.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2574,7 +2590,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2599,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>850</v>
+        <v>270</v>
       </c>
       <c r="Q23" t="n">
-        <v>598</v>
+        <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>1448</v>
+        <v>282</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2614,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1141861707</t>
+          <t>20343581</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141861707</t>
+          <t>https://m.place.naver.com/place/20343581</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2620,39 +2636,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>서울예미인피부과의원</t>
+          <t>아름다운나라피부과의원 분당</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yemein_bdh@naver.com</t>
+          <t>anaderma@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>031-711-0280</t>
+          <t>031-707-0878</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 BYC건물 2층</t>
+          <t>경기도 성남시 분당구 황새울로 332 분당문화센터 6층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://yemein.com/</t>
+          <t>https://blog.naver.com/anaderma</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2673,17 +2689,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>562</v>
+        <v>373</v>
       </c>
       <c r="Q24" t="n">
-        <v>221</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>783</v>
+        <v>381</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2708,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13032291</t>
+          <t>13517048</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13032291</t>
+          <t>https://m.place.naver.com/place/13517048</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2714,34 +2730,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오브디의원</t>
+          <t>벨리에의원</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dr_kkang@naver.com</t>
+          <t>bundangsb@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1383-5702</t>
+          <t>0507-1428-5859</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 젤존타워1 5층 510호 오브디의원</t>
+          <t>경기도 성남시 분당구 황새울로 340 5층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dr_kkang</t>
+          <t>http://bellierclinic.com</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2751,7 +2767,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2762,7 +2778,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2771,13 +2787,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>291</v>
+        <v>962</v>
       </c>
       <c r="Q25" t="n">
-        <v>2869</v>
+        <v>384</v>
       </c>
       <c r="R25" t="n">
-        <v>3160</v>
+        <v>1346</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2802,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1260816786</t>
+          <t>1362445992</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260816786</t>
+          <t>https://m.place.naver.com/place/1362445992</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2808,44 +2824,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>휴먼피부과의원 분당점</t>
+          <t>에스앤유피부과의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dermr@naver.com</t>
+          <t>abeer4u@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>031-713-9995</t>
+          <t>031-714-0808</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 97 다운타운 304호</t>
+          <t>경기도 성남시 분당구 황새울로200번길 9-7 판테온 빌딩 2층 에스앤유피부과</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://humanbd.co.kr/</t>
+          <t>https://blog.naver.com/abeer4u</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2856,22 +2872,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Q26" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
-        <v>432</v>
+        <v>181</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2896,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1452441194</t>
+          <t>13186238</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452441194</t>
+          <t>https://m.place.naver.com/place/13186238</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2902,29 +2918,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>뷰티라운지의원 판교점</t>
+          <t>삼성맑은피부과의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>beautyloungeclinic@naver.com</t>
+          <t>sspureclinic@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-698-3727</t>
+          <t>031-698-4016</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움타워 2동 지하1층 뷰티라운지의원</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 4층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pangyo.beautyloungeclinic.com/</t>
+          <t>http://sspureclinic.com</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2959,13 +2975,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>549</v>
+        <v>453</v>
       </c>
       <c r="Q27" t="n">
-        <v>2289</v>
+        <v>206</v>
       </c>
       <c r="R27" t="n">
-        <v>2838</v>
+        <v>659</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2990,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1742515435</t>
+          <t>1582994500</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742515435</t>
+          <t>https://m.place.naver.com/place/1582994500</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2996,29 +3012,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>베네핏의원</t>
+          <t>유앤아이피부과의원 분당미금점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>benefitclinic-@naver.com</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>wldnjs8802@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mdvision@nate.com</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>031-778-8253</t>
+          <t>031-8039-6021</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 2층</t>
+          <t>경기도 성남시 분당구 돌마로 86 엘레강스프라자 2동 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://benefitclinic.co.kr</t>
+          <t>https://www.bmuni114.co.kr/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3033,7 +3053,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3053,13 +3073,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>330</v>
+        <v>1040</v>
       </c>
       <c r="Q28" t="n">
-        <v>2878</v>
+        <v>2981</v>
       </c>
       <c r="R28" t="n">
-        <v>3208</v>
+        <v>4021</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3088,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1034660593</t>
+          <t>2063670518</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034660593</t>
+          <t>https://m.place.naver.com/place/2063670518</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3090,34 +3110,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>미소앤의원</t>
+          <t>메이퓨어의원 야탑점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>misoenclinic@naver.com</t>
+          <t>minday123@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1495-7478</t>
+          <t>031-399-9990</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 168 미도프라자 6층 601호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 6층 608호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/misoenclinic</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3127,7 +3147,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3138,22 +3158,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>156</v>
+        <v>2466</v>
       </c>
       <c r="Q29" t="n">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
-        <v>294</v>
+        <v>2490</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3182,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1467523840</t>
+          <t>36654949</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467523840</t>
+          <t>https://m.place.naver.com/place/36654949</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3184,29 +3204,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>유앤아이피부과의원 판교점</t>
+          <t>더에이치의원 분당</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jccbtfu_411@naver.com</t>
+          <t>macclinic7061@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>031-8016-6020</t>
+          <t>0507-1357-7061</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 12 판교미래에셋센터 2층 202, 203호</t>
+          <t>경기도 성남시 분당구 돌마로 75 4층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.pguni114.co.kr/</t>
+          <t>http://thehclinic.ad-media.kr</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3216,12 +3236,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3232,7 +3252,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3241,13 +3261,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1051</v>
+        <v>176</v>
       </c>
       <c r="Q30" t="n">
-        <v>1794</v>
+        <v>1274</v>
       </c>
       <c r="R30" t="n">
-        <v>2845</v>
+        <v>1450</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3276,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>19759020</t>
+          <t>1828034209</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19759020</t>
+          <t>https://m.place.naver.com/place/1828034209</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3278,39 +3298,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>닥터스피부과의원 서판교</t>
+          <t>비타민의원 분당점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>doctorspg@naver.com</t>
+          <t>vitaderm@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-698-3088</t>
+          <t>0507-1481-0298</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 237 2층</t>
+          <t>경기도 성남시 분당구 서현로210번길 2 3층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://seopangyo.doctors365.co.kr</t>
+          <t>http://www.vitaminclinic.kr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3335,13 +3355,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="Q31" t="n">
-        <v>86</v>
+        <v>5393</v>
       </c>
       <c r="R31" t="n">
-        <v>406</v>
+        <v>5705</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3370,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1937925934</t>
+          <t>13182156</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1937925934</t>
+          <t>https://m.place.naver.com/place/13182156</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3372,44 +3392,48 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>리즈피부과의원</t>
+          <t>유앤아이피부과의원 판교점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>leeskin2005@naver.com</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>jccbtfu_411@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>mdvision@nate.com</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>031-713-3553</t>
+          <t>031-8016-6020</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존타워III 4층 403호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 12 판교미래에셋센터 2층 202, 203호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leeskin2005</t>
+          <t>https://www.pguni114.co.kr/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3420,22 +3444,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>276</v>
+        <v>1049</v>
       </c>
       <c r="Q32" t="n">
-        <v>324</v>
+        <v>1621</v>
       </c>
       <c r="R32" t="n">
-        <v>600</v>
+        <v>2670</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3468,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>20762481</t>
+          <t>19759020</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20762481</t>
+          <t>https://m.place.naver.com/place/19759020</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3490,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>심덕택피부과의원</t>
+          <t>톤즈의원 분당</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0x0030@naver.com</t>
+          <t>tones_bundang@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>031-716-1353</t>
+          <t>0507-1489-5804</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 306호</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 225호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.goldskin.co.kr/</t>
+          <t>https://tonesclinic.co.kr/bundang</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3514,22 +3538,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1247</v>
+        <v>2479</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>7507</v>
       </c>
       <c r="R33" t="n">
-        <v>1262</v>
+        <v>9986</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3562,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11719317</t>
+          <t>1049120141</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11719317</t>
+          <t>https://m.place.naver.com/place/1049120141</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3560,34 +3584,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>늘샤인의원</t>
+          <t>분당동안의원</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>asclinic@naver.com</t>
+          <t>pix1246@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1481-7894</t>
+          <t>031-708-0822</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 11 글라스타워 3층 늘샤인의원</t>
+          <t>경기도 성남시 분당구 황새울로360번길 35 현대프라자 4층 407호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://alwaysshineclinic.com</t>
+          <t>http://www.donganclinicbd.com/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3617,13 +3641,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q34" t="n">
-        <v>3234</v>
+        <v>1648</v>
       </c>
       <c r="R34" t="n">
-        <v>3748</v>
+        <v>2160</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,17 +3656,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1606161160</t>
+          <t>12943172</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1606161160</t>
+          <t>https://m.place.naver.com/place/12943172</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3654,35 +3678,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>바른피부과의원</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>유어라인의원</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>yourlineclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1407-5500</t>
+          <t>031-715-3657</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 435 동양프라자 305호 바른피부과의원</t>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 5층 503호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xfxexdxhn</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3698,19 +3726,19 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="R35" t="n">
         <v>233</v>
@@ -3722,17 +3750,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1045465077</t>
+          <t>1898979899</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045465077</t>
+          <t>https://m.place.naver.com/place/1898979899</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3744,39 +3772,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>힐하우스피부과의원 판교점</t>
+          <t>메이저피부과의원 분당점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>healhousepg@naver.com</t>
+          <t>bonpibu@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1358-7438</t>
+          <t>0507-1389-7345</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 131 2층</t>
+          <t>경기도 성남시 분당구 황새울로351번길 10 여암빌딩 3층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.healhousepg.com/</t>
+          <t>https://blog.naver.com/bonpibu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3792,22 +3820,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="Q36" t="n">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="R36" t="n">
-        <v>592</v>
+        <v>426</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3844,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1245847654</t>
+          <t>19782204</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245847654</t>
+          <t>https://m.place.naver.com/place/19782204</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3838,39 +3866,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>다시봄날의원 분당</t>
+          <t>파인트리피부과의원</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>yesokkim0510@naver.com</t>
+          <t>pinetree_derma_@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1488-7676</t>
+          <t>0507-1373-2095</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 제5층 501-2호</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 5층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://bd.springdayclinic.com/</t>
+          <t>https://blog.naver.com/pinetree_derma_</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3886,7 +3914,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3895,13 +3923,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>921</v>
+        <v>285</v>
       </c>
       <c r="Q37" t="n">
-        <v>5010</v>
+        <v>319</v>
       </c>
       <c r="R37" t="n">
-        <v>5931</v>
+        <v>604</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +3938,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1986908099</t>
+          <t>1319261524</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986908099</t>
+          <t>https://m.place.naver.com/place/1319261524</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3932,33 +3960,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>필로의원 분당</t>
+          <t>휴먼피부과의원 분당점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>reply1879@naver.com</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>drjiyoonh@gmail.com</t>
-        </is>
-      </c>
+          <t>dermr@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1377-3501</t>
+          <t>031-713-9995</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 15 제나프라자 7층</t>
+          <t>경기도 성남시 분당구 백현로 97 다운타운 304호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pilloclinic.com</t>
+          <t>https://humanbd.co.kr/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3993,13 +4017,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>605</v>
+        <v>175</v>
       </c>
       <c r="Q38" t="n">
-        <v>2866</v>
+        <v>259</v>
       </c>
       <c r="R38" t="n">
-        <v>3471</v>
+        <v>434</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4032,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1387995733</t>
+          <t>1452441194</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1387995733</t>
+          <t>https://m.place.naver.com/place/1452441194</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4030,29 +4054,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>분당프리미어의원</t>
+          <t>파랑새피부과의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>isigary@naver.com</t>
+          <t>bluebirdskin@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1405-7918</t>
+          <t>0507-1319-4171</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 29 2층</t>
+          <t>경기도 성남시 분당구 수내로 39 2층 236호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/isigary</t>
+          <t>https://blog.naver.com/bluebirdskin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4087,13 +4111,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>612</v>
+        <v>281</v>
       </c>
       <c r="Q39" t="n">
-        <v>4797</v>
+        <v>336</v>
       </c>
       <c r="R39" t="n">
-        <v>5409</v>
+        <v>617</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4126,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1095182275</t>
+          <t>1340499564</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095182275</t>
+          <t>https://m.place.naver.com/place/1340499564</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4124,34 +4148,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>리셋의원 분당</t>
+          <t>메디큐브의원 분당서현</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>resetclinic_official@naver.com</t>
+          <t>yaguchenjae@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1362-6644</t>
+          <t>0507-1325-6277</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 21 5층</t>
+          <t>경기도 성남시 분당구 황새울로 326 분당서현빌딩 별관 4층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbsWQj</t>
+          <t>http://www.medicubesignature.com</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4172,7 +4196,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4181,13 +4205,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>977</v>
+        <v>2429</v>
       </c>
       <c r="Q40" t="n">
-        <v>5129</v>
+        <v>800</v>
       </c>
       <c r="R40" t="n">
-        <v>6106</v>
+        <v>3229</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4220,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1708856210</t>
+          <t>1907560612</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708856210</t>
+          <t>https://m.place.naver.com/place/1907560612</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4218,29 +4242,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>아비쥬의원 분당</t>
+          <t>늘샤인의원</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hj_4326@naver.com</t>
+          <t>asclinic@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>031-607-1717</t>
+          <t>0507-1481-7894</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 10 동호프라자 401호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 11 글라스타워 3층 늘샤인의원</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hj_4326</t>
+          <t>http://alwaysshineclinic.com</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,7 +4274,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4266,7 +4290,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4275,13 +4299,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2126</v>
+        <v>516</v>
       </c>
       <c r="Q41" t="n">
-        <v>160</v>
+        <v>3194</v>
       </c>
       <c r="R41" t="n">
-        <v>2286</v>
+        <v>3710</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4314,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1202847355</t>
+          <t>1606161160</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202847355</t>
+          <t>https://m.place.naver.com/place/1606161160</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4312,29 +4336,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>에스앤유피부과의원</t>
+          <t>연세모네피부과의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abeer4u@naver.com</t>
+          <t>ghjk316@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>031-714-0808</t>
+          <t>031-709-6354</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로200번길 9-7 판테온 빌딩 2층 에스앤유피부과</t>
+          <t>경기도 성남시 분당구 분당로53번길 22 블루홀플라자</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/abeer4u</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4344,12 +4368,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4369,13 +4393,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R42" t="n">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4408,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>13186238</t>
+          <t>11538782</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13186238</t>
+          <t>https://m.place.naver.com/place/11538782</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4406,29 +4430,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>톤즈의원 분당</t>
+          <t>미금밴스의원</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tones_bundang@naver.com</t>
+          <t>ilove4145@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1489-5804</t>
+          <t>031-778-8037</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 225호</t>
+          <t>경기도 성남시 분당구 돌마로 86 엘레강스프라자B동 8층 801호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://tonesclinic.co.kr/bundang</t>
+          <t>https://migeum.vandsclinic.co.kr/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4443,7 +4467,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4459,17 +4483,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2443</v>
+        <v>871</v>
       </c>
       <c r="Q43" t="n">
-        <v>7211</v>
+        <v>600</v>
       </c>
       <c r="R43" t="n">
-        <v>9654</v>
+        <v>1471</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,17 +4502,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1049120141</t>
+          <t>1141861707</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049120141</t>
+          <t>https://m.place.naver.com/place/1141861707</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4500,34 +4524,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>리뉴미피부과의원 분당</t>
+          <t>리셋의원 분당</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mdderma@naver.com</t>
+          <t>resetclinic_official@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>031-711-6711</t>
+          <t>0507-1362-6644</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-3 여민빌딩 4층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 21 5층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mdderma</t>
+          <t>http://pf.kakao.com/_xbsWQj</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4537,7 +4561,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4548,7 +4572,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4557,13 +4581,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>833</v>
+        <v>977</v>
       </c>
       <c r="Q44" t="n">
-        <v>148</v>
+        <v>4905</v>
       </c>
       <c r="R44" t="n">
-        <v>981</v>
+        <v>5882</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4572,17 +4596,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>36432617</t>
+          <t>1708856210</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36432617</t>
+          <t>https://m.place.naver.com/place/1708856210</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4594,25 +4618,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>분당판교 아르버의원</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>로즈피부과 분당점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>roseclinic_@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1386-3591</t>
+          <t>0507-1437-9970</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로 84 2층 202호</t>
+          <t>경기도 성남시 분당구 느티로 27 하나프라자 6층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://arborclinic.kr</t>
+          <t>http://www.roseclinic.kr/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4647,13 +4675,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="Q45" t="n">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="R45" t="n">
-        <v>325</v>
+        <v>420</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,17 +4690,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2010135298</t>
+          <t>12952311</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010135298</t>
+          <t>https://m.place.naver.com/place/12952311</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4684,39 +4712,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>분당닥터에버스의원</t>
+          <t>리뉴미피부과의원 분당</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>77bundang@naver.com</t>
+          <t>mdderma@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1389-7537</t>
+          <t>031-711-6711</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 35 서현현대프라자 3층 304호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-3 여민빌딩 4층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.evers29.co.kr/</t>
+          <t>https://blog.naver.com/mdderma</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4732,7 +4760,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4741,13 +4769,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>150</v>
+        <v>833</v>
       </c>
       <c r="Q46" t="n">
-        <v>391</v>
+        <v>148</v>
       </c>
       <c r="R46" t="n">
-        <v>541</v>
+        <v>981</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,17 +4784,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1100909582</t>
+          <t>36432617</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100909582</t>
+          <t>https://m.place.naver.com/place/36432617</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4778,44 +4806,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>메디큐브의원 분당서현</t>
+          <t>아젤린의원 정자</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>yaguchenjae@naver.com</t>
+          <t>azelin-bundang@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1325-6277</t>
+          <t>0507-1383-1745</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 326 분당서현빌딩 별관 4층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존타워3 3층 306호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.medicubesignature.com</t>
+          <t>http://www.azelin.co.kr/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4826,7 +4854,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4835,13 +4863,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2427</v>
+        <v>865</v>
       </c>
       <c r="Q47" t="n">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="R47" t="n">
-        <v>3224</v>
+        <v>1682</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,17 +4878,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1907560612</t>
+          <t>37745081</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907560612</t>
+          <t>https://m.place.naver.com/place/37745081</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4872,29 +4900,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>아름다운나라피부과의원 분당</t>
+          <t>이봉구피부과의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>anaderma@naver.com</t>
+          <t>demiann-@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>031-707-0878</t>
+          <t>031-711-1213</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 분당문화센터 6층</t>
+          <t>경기도 성남시 분당구 내정로 170 동신파크빌딩 304호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anaderma</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4904,12 +4932,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4925,17 +4953,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>373</v>
+        <v>648</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="R48" t="n">
-        <v>381</v>
+        <v>679</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,17 +4972,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13517048</t>
+          <t>13036099</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13517048</t>
+          <t>https://m.place.naver.com/place/13036099</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4966,34 +4994,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>메이저피부과의원 분당점</t>
+          <t>미금메이퓨어의원</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bonpibu@naver.com</t>
+          <t>buggmi33@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1389-7345</t>
+          <t>031-715-9960</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로351번길 10 여암빌딩 3층</t>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bonpibu</t>
+          <t>https://www.maypureclinic.com/community/migeum</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5003,7 +5031,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5019,17 +5047,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>225</v>
+        <v>2505</v>
       </c>
       <c r="Q49" t="n">
-        <v>193</v>
+        <v>2151</v>
       </c>
       <c r="R49" t="n">
-        <v>418</v>
+        <v>4656</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,17 +5066,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>19782204</t>
+          <t>593028781</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19782204</t>
+          <t>https://m.place.naver.com/place/593028781</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5060,34 +5088,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>차앤박피부과의원 분당서현점</t>
+          <t>진스킨의원</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cnpsh7229@naver.com</t>
+          <t>zinskin1@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>031-709-7229</t>
+          <t>0507-1446-1061</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 9 정현빌딩 8층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 6층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://www.cnpskin.co.kr/hos/main.php?groupid=cnpskin09</t>
+          <t>http://www.zinskin.com/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5113,17 +5141,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>347</v>
+        <v>422</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>409</v>
       </c>
       <c r="R50" t="n">
-        <v>401</v>
+        <v>831</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,17 +5160,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>11696898</t>
+          <t>33136407</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11696898</t>
+          <t>https://m.place.naver.com/place/33136407</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5154,29 +5182,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>포에버의원 분당</t>
+          <t>필로의원 분당</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4everbun@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>reply1879@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>drjiyoonh@gmail.com</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1365-8348</t>
+          <t>0507-1377-3501</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 15 제나프라자 7층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://bd.4-ever.co.kr</t>
+          <t>http://pilloclinic.com</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5191,7 +5223,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5211,13 +5243,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>981</v>
+        <v>606</v>
       </c>
       <c r="Q51" t="n">
-        <v>3148</v>
+        <v>3004</v>
       </c>
       <c r="R51" t="n">
-        <v>4129</v>
+        <v>3610</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5226,17 +5258,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>20747205</t>
+          <t>1387995733</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20747205</t>
+          <t>https://m.place.naver.com/place/1387995733</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5248,30 +5280,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>유앤아이피부과의원 분당미금점</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>바른피부과의원</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gp3465@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>031-8039-6021</t>
+          <t>0507-1407-5500</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 86 엘레강스프라자 2동 2층</t>
+          <t>경기도 성남시 분당구 판교로 435 동양프라자 305호 바른피부과의원</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.bmuni114.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5297,17 +5333,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1016</v>
+        <v>229</v>
       </c>
       <c r="Q52" t="n">
-        <v>2930</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>3946</v>
+        <v>233</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5352,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2063670518</t>
+          <t>1045465077</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2063670518</t>
+          <t>https://m.place.naver.com/place/1045465077</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5338,34 +5374,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>휴피부과 의원</t>
+          <t>서울예미인피부과의원</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>yshue1216@naver.com</t>
+          <t>atidarch@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>031-701-1093</t>
+          <t>031-711-0280</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워</t>
+          <t>경기도 성남시 분당구 성남대로 912 BYC건물 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://yemein.com/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5375,7 +5411,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5395,13 +5431,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>664</v>
+        <v>563</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="R53" t="n">
-        <v>676</v>
+        <v>788</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5446,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>21056684</t>
+          <t>13032291</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21056684</t>
+          <t>https://m.place.naver.com/place/13032291</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5432,44 +5468,44 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>루이의원</t>
+          <t>스킨영의원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>louisclinic-4008@naver.com</t>
+          <t>yumin3115@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1398-4009</t>
+          <t>031-716-3337</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 3층</t>
+          <t>경기도 성남시 분당구 백현로101번길 17 초림프라자 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://louisclinic.com/</t>
+          <t>https://blog.naver.com/yumin3115</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5489,13 +5525,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>404</v>
+        <v>951</v>
       </c>
       <c r="Q54" t="n">
-        <v>2424</v>
+        <v>1538</v>
       </c>
       <c r="R54" t="n">
-        <v>2828</v>
+        <v>2489</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,17 +5540,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>36428162</t>
+          <t>1461069782</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428162</t>
+          <t>https://m.place.naver.com/place/1461069782</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5526,39 +5562,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>티앤티의원</t>
+          <t>샤인유의원 분당</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>fatrasue@naver.com</t>
+          <t>madeu_bd@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>031-608-0085</t>
+          <t>031-698-2555</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 12 5층</t>
+          <t>경기도 성남시 분당구 황새울로312번길 5 세광빌딩 3층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://tntclinic.kr/</t>
+          <t>https://blog.naver.com/madeu_bd</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5574,7 +5610,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5583,13 +5619,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1463</v>
+        <v>674</v>
       </c>
       <c r="Q55" t="n">
-        <v>3013</v>
+        <v>321</v>
       </c>
       <c r="R55" t="n">
-        <v>4476</v>
+        <v>995</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5634,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1778414883</t>
+          <t>1973024753</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1778414883</t>
+          <t>https://m.place.naver.com/place/1973024753</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5620,30 +5656,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>리즈온의원 분당</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>분당판교 아르버의원</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>chocosoyeon@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>031-705-0870</t>
+          <t>0507-1386-3591</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 11 4층</t>
+          <t>경기도 성남시 분당구 판교대장로 84 2층 202호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://bundang.lizonclinic.co.kr</t>
+          <t>https://arborclinic.kr</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5653,7 +5693,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5669,17 +5709,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1051</v>
+        <v>170</v>
       </c>
       <c r="Q56" t="n">
-        <v>2614</v>
+        <v>162</v>
       </c>
       <c r="R56" t="n">
-        <v>3665</v>
+        <v>332</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5728,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1231128843</t>
+          <t>2010135298</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231128843</t>
+          <t>https://m.place.naver.com/place/2010135298</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5710,29 +5750,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오라클피부과의원 분당서현점</t>
+          <t>판교연세피부과의원</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>oraclebd02@naver.com</t>
+          <t>thewisepine@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>031-707-4975</t>
+          <t>031-8017-5252</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 서현프라자6층</t>
+          <t>경기도 성남시 분당구 동판교로 59 자유퍼스트프라자 1동 301호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oraclebd02</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5742,12 +5782,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5767,13 +5807,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>890</v>
+        <v>250</v>
       </c>
       <c r="Q57" t="n">
-        <v>295</v>
+        <v>12</v>
       </c>
       <c r="R57" t="n">
-        <v>1185</v>
+        <v>262</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5822,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11725308</t>
+          <t>21423768</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11725308</t>
+          <t>https://m.place.naver.com/place/21423768</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5804,39 +5844,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>파인트리피부과의원</t>
+          <t>베네핏의원</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pinetree_derma_@naver.com</t>
+          <t>benefitclinic-@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1373-2095</t>
+          <t>031-778-8253</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 5층</t>
+          <t>경기도 성남시 분당구 성남대로 151 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pinetree_derma_</t>
+          <t>http://benefitclinic.co.kr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5852,7 +5892,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5861,13 +5901,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="Q58" t="n">
-        <v>314</v>
+        <v>2937</v>
       </c>
       <c r="R58" t="n">
-        <v>596</v>
+        <v>3270</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5916,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1319261524</t>
+          <t>1034660593</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319261524</t>
+          <t>https://m.place.naver.com/place/1034660593</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5898,39 +5938,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CNP차앤박피부과의원 분당 정자</t>
+          <t>오월의아침피부과의원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cnpskinjj@naver.com</t>
+          <t>maymorning_05@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>031-715-0061</t>
+          <t>031-717-5207</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-13</t>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 5층 오월의아침피부과의원</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cnpskinjj</t>
+          <t>http://www.maymorning.kr/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5946,22 +5986,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>210</v>
+        <v>501</v>
       </c>
       <c r="Q59" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="R59" t="n">
-        <v>328</v>
+        <v>609</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +6010,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11696919</t>
+          <t>12771235</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11696919</t>
+          <t>https://m.place.naver.com/place/12771235</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5992,44 +6032,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>분당예쁨주의쁨의원</t>
+          <t>차앤박피부과의원 분당서현점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jlles1@naver.com</t>
+          <t>cnpsh7229@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>031-703-3010</t>
+          <t>031-709-7229</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 12 서현 나산플라자 4층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 9 정현빌딩 8층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.ppeum10.com</t>
+          <t>http://www.cnpskin.co.kr/hos/main.php?groupid=cnpskin09</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6049,13 +6089,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>864</v>
+        <v>348</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="R60" t="n">
-        <v>881</v>
+        <v>402</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6064,17 +6104,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1028564181</t>
+          <t>11696898</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028564181</t>
+          <t>https://m.place.naver.com/place/11696898</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6086,29 +6126,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>진스킨의원</t>
+          <t>오라클피부과의원 분당서현점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>zinskin1@naver.com</t>
+          <t>oraclebd02@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1446-1061</t>
+          <t>031-707-4975</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 6층</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 서현프라자6층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.zinskin.com/</t>
+          <t>https://blog.naver.com/oraclebd02</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6118,7 +6158,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6134,22 +6174,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>401</v>
+        <v>893</v>
       </c>
       <c r="Q61" t="n">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="R61" t="n">
-        <v>806</v>
+        <v>1188</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6158,17 +6198,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>33136407</t>
+          <t>11725308</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33136407</t>
+          <t>https://m.place.naver.com/place/11725308</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6180,29 +6220,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>스킨영의원</t>
+          <t>분당정자 셀린의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>yumin3115@naver.com</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>cellinclinic-bundang@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>webtick@gmail.com</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>031-716-3337</t>
+          <t>031-1833-6372</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 17 초림프라자 2층</t>
+          <t>경기도 성남시 분당구 성남대로 349 301호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yumin3115</t>
+          <t>https://www.cellinclinic10.com/clinicInfoCellin/selfReserve.php</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6212,12 +6256,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6237,13 +6281,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>949</v>
+        <v>1015</v>
       </c>
       <c r="Q62" t="n">
-        <v>1489</v>
+        <v>4894</v>
       </c>
       <c r="R62" t="n">
-        <v>2438</v>
+        <v>5909</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6252,17 +6296,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1461069782</t>
+          <t>1159993527</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461069782</t>
+          <t>https://m.place.naver.com/place/1159993527</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6274,34 +6318,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>미금메이퓨어의원</t>
+          <t>미앤미의원 분당</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>buggmi33@naver.com</t>
+          <t>asubtend@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>031-715-9960</t>
+          <t>031-704-1171</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 분당서현신영팰리스타워 4층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/community/migeum</t>
+          <t>https://blog.naver.com/asubtend</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6311,7 +6355,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6331,13 +6375,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2483</v>
+        <v>742</v>
       </c>
       <c r="Q63" t="n">
-        <v>2091</v>
+        <v>5401</v>
       </c>
       <c r="R63" t="n">
-        <v>4574</v>
+        <v>6143</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,17 +6390,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>593028781</t>
+          <t>37341394</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/593028781</t>
+          <t>https://m.place.naver.com/place/37341394</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6368,29 +6412,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>이봉구피부과의원</t>
+          <t>분당예쁨주의쁨의원</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jjondgi@naver.com</t>
+          <t>jlles1@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>031-711-1213</t>
+          <t>031-703-3010</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로 170 동신파크빌딩 304호</t>
+          <t>경기도 성남시 분당구 분당로53번길 12 서현 나산플라자 4층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.ppeum10.com</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6400,7 +6444,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6421,17 +6465,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>648</v>
+        <v>869</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="R64" t="n">
-        <v>680</v>
+        <v>886</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6440,17 +6484,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>13036099</t>
+          <t>1028564181</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13036099</t>
+          <t>https://m.place.naver.com/place/1028564181</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6462,29 +6506,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>유앤미의원 분당점</t>
+          <t>리즈온의원 분당</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bdunme@naver.com</t>
+          <t>daru0527@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1331-9931</t>
+          <t>031-705-0870</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 19 피아자코코빌딩 4층</t>
+          <t>경기도 성남시 분당구 분당로53번길 11 4층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://www.bundangyounme.co.kr/</t>
+          <t>https://bundang.lizonclinic.co.kr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6494,12 +6538,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6510,22 +6554,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>189</v>
+        <v>1071</v>
       </c>
       <c r="Q65" t="n">
-        <v>730</v>
+        <v>2616</v>
       </c>
       <c r="R65" t="n">
-        <v>919</v>
+        <v>3687</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6534,17 +6578,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>37553792</t>
+          <t>1231128843</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37553792</t>
+          <t>https://m.place.naver.com/place/1231128843</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6556,30 +6600,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>블리비의원 분당점</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>데이뷰의원 분당점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nextday92@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1833-3130</t>
+          <t>0507-1395-8031</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 2 성지하이츠텔 2층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자3 2층 206호, 207호, 211호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.velyb.kr/</t>
+          <t>https://www.daybeauclinic12.com</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6609,13 +6657,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1336</v>
+        <v>3057</v>
       </c>
       <c r="Q66" t="n">
-        <v>2895</v>
+        <v>11075</v>
       </c>
       <c r="R66" t="n">
-        <v>4231</v>
+        <v>14132</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6624,17 +6672,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2076023323</t>
+          <t>1094772288</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076023323</t>
+          <t>https://m.place.naver.com/place/1094772288</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6646,29 +6694,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>파랑새피부과의원</t>
+          <t>리버스의원 분당</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bluebirdskin@naver.com</t>
+          <t>cap0153@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1319-4171</t>
+          <t>0507-1377-7086</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 39 2층 236호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 19 2층 201, 202호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bluebirdskin</t>
+          <t>https://bd.reverseclinic.com/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6694,7 +6742,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6703,13 +6751,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>280</v>
+        <v>1031</v>
       </c>
       <c r="Q67" t="n">
-        <v>336</v>
+        <v>832</v>
       </c>
       <c r="R67" t="n">
-        <v>616</v>
+        <v>1863</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6718,17 +6766,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1340499564</t>
+          <t>2099954204</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340499564</t>
+          <t>https://m.place.naver.com/place/2099954204</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6740,40 +6788,48 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>벨리에의원</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+          <t>리더스피부과의원 판교</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>leaderspgd@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>master@beautyleader.co.kr</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1428-5859</t>
+          <t>031-8023-5085</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 340 5층</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 판교리더스피부과</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://bellierclinic.com</t>
+          <t>https://leaders-pg.com/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6793,13 +6849,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>960</v>
+        <v>421</v>
       </c>
       <c r="Q68" t="n">
-        <v>379</v>
+        <v>1426</v>
       </c>
       <c r="R68" t="n">
-        <v>1339</v>
+        <v>1847</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6808,17 +6864,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1362445992</t>
+          <t>21697693</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1362445992</t>
+          <t>https://m.place.naver.com/place/21697693</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6830,34 +6886,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>미앤미의원 분당</t>
+          <t>수내메이퓨어의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>asubtend@naver.com</t>
+          <t>8832707@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>031-704-1171</t>
+          <t>031-717-3336</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 분당서현신영팰리스타워 4층</t>
+          <t>경기도 성남시 분당구 백현로 97 수내동 다운타운 1004호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/asubtend</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6867,7 +6923,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6878,22 +6934,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>728</v>
+        <v>1063</v>
       </c>
       <c r="Q69" t="n">
-        <v>5478</v>
+        <v>34</v>
       </c>
       <c r="R69" t="n">
-        <v>6206</v>
+        <v>1097</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6902,17 +6958,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>37341394</t>
+          <t>1638817358</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37341394</t>
+          <t>https://m.place.naver.com/place/1638817358</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6924,29 +6980,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>야탑밴스의원</t>
+          <t>분당 맥스웰의원</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>y_yse0@naver.com</t>
+          <t>hazy_920726@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>031-778-8828</t>
+          <t>031-717-5824</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 604호, 605호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 7 301호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://yatap.vandsclinic.co.kr/</t>
+          <t>http://bundang.maxwellhair.com/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6972,22 +7028,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1125</v>
+        <v>96</v>
       </c>
       <c r="Q70" t="n">
-        <v>4722</v>
+        <v>12</v>
       </c>
       <c r="R70" t="n">
-        <v>5847</v>
+        <v>108</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6996,17 +7052,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1733838797</t>
+          <t>1494157050</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1733838797</t>
+          <t>https://m.place.naver.com/place/1494157050</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7018,29 +7074,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>포레스트의원</t>
+          <t>심덕택피부과의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>forest_derma@naver.com</t>
+          <t>0x0030@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1343-3890</t>
+          <t>031-716-1353</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로335번길 5 N타운빌딩 4층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 306호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://forest.quv.kr</t>
+          <t>http://www.goldskin.co.kr/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7066,22 +7122,22 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>587</v>
+        <v>1247</v>
       </c>
       <c r="Q71" t="n">
-        <v>6266</v>
+        <v>15</v>
       </c>
       <c r="R71" t="n">
-        <v>6853</v>
+        <v>1262</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7090,17 +7146,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>32430482</t>
+          <t>11719317</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32430482</t>
+          <t>https://m.place.naver.com/place/11719317</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7112,29 +7168,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>분당정자 셀린의원</t>
+          <t>야탑밴스의원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>cellinclinic-bundang@naver.com</t>
+          <t>y_yse0@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>031-1833-6372</t>
+          <t>031-778-8828</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 349 301호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 604호, 605호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.cellinclinic10.com/clinicInfoCellin/selfReserve.php</t>
+          <t>https://yatap.vandsclinic.co.kr/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7165,17 +7221,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1005</v>
+        <v>1144</v>
       </c>
       <c r="Q72" t="n">
-        <v>5438</v>
+        <v>4550</v>
       </c>
       <c r="R72" t="n">
-        <v>6443</v>
+        <v>5694</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7184,17 +7240,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1159993527</t>
+          <t>1733838797</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159993527</t>
+          <t>https://m.place.naver.com/place/1733838797</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7206,29 +7262,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>더에이치의원 분당</t>
+          <t>분당닥터에버스의원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>macclinic7061@naver.com</t>
+          <t>77bundang@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1357-7061</t>
+          <t>0507-1389-7537</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 4층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 35 서현현대프라자 3층 304호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://thehclinic.ad-media.kr</t>
+          <t>https://www.evers29.co.kr/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7263,13 +7319,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Q73" t="n">
-        <v>1473</v>
+        <v>434</v>
       </c>
       <c r="R73" t="n">
-        <v>1649</v>
+        <v>602</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7278,17 +7334,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1828034209</t>
+          <t>1100909582</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828034209</t>
+          <t>https://m.place.naver.com/place/1100909582</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7300,29 +7356,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>비타민의원 분당점</t>
+          <t>힐하우스피부과의원 판교점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>vitaderm@naver.com</t>
+          <t>healhousepg@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1481-0298</t>
+          <t>0507-1358-7438</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 2 3층</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://www.vitaminclinic.kr</t>
+          <t>https://www.healhousepg.com/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7337,7 +7393,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7357,13 +7413,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="Q74" t="n">
-        <v>5830</v>
+        <v>307</v>
       </c>
       <c r="R74" t="n">
-        <v>6142</v>
+        <v>599</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7372,17 +7428,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>13182156</t>
+          <t>1245847654</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13182156</t>
+          <t>https://m.place.naver.com/place/1245847654</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7394,29 +7450,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>리버스의원 분당</t>
+          <t>분당 톡스앤필의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ups126@naver.com</t>
+          <t>toxnfill5@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1377-7086</t>
+          <t>031-707-3500</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 19 2층 201, 202호</t>
+          <t>경기도 성남시 분당구 성남대로343번길 12-2 5층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://bd.reverseclinic.com/</t>
+          <t>https://www.toxnfill5.com</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7426,7 +7482,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7451,13 +7507,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1031</v>
+        <v>826</v>
       </c>
       <c r="Q75" t="n">
-        <v>828</v>
+        <v>5719</v>
       </c>
       <c r="R75" t="n">
-        <v>1859</v>
+        <v>6545</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7466,17 +7522,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2099954204</t>
+          <t>1299969468</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099954204</t>
+          <t>https://m.place.naver.com/place/1299969468</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7488,29 +7544,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>데이뷰의원 분당점</t>
+          <t>메이린의원 판교</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nextday92@naver.com</t>
+          <t>pangyomaylin@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1395-8031</t>
+          <t>0507-1301-3246</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자3 2층 206호, 207호, 211호</t>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 10층 메이린클리닉 판교점</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.daybeauclinic12.com</t>
+          <t>https://www.instagram.com/maylinclinic_pg/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7520,7 +7576,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7536,7 +7592,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7545,13 +7601,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2971</v>
+        <v>118</v>
       </c>
       <c r="Q76" t="n">
-        <v>11539</v>
+        <v>147</v>
       </c>
       <c r="R76" t="n">
-        <v>14510</v>
+        <v>265</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7560,17 +7616,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1094772288</t>
+          <t>37035893</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094772288</t>
+          <t>https://m.place.naver.com/place/37035893</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_derma/분당_피부과.xlsx
+++ b/naver-place-crawler/results_derma/분당_피부과.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>박병찬피부과의원</t>
+          <t>아이린피부과의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>et941104@naver.com</t>
+          <t>redmt0909@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-719-5500</t>
+          <t>031-719-7525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로165번길 50 3층</t>
+          <t>경기도 성남시 분당구 성남대로 345</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.ireneskin.com/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>165</v>
+        <v>389</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>337</v>
       </c>
       <c r="R2" t="n">
-        <v>170</v>
+        <v>726</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13234870</t>
+          <t>19494195</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13234870</t>
+          <t>https://m.place.naver.com/place/19494195</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>분당프리미어의원</t>
+          <t>링클스탑의원 분당서현</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>isigary@naver.com</t>
+          <t>wrinklestop@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1405-7918</t>
+          <t>0507-1341-0516</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 29 2층</t>
+          <t>경기도 성남시 분당구 서현로 184 217호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/isigary</t>
+          <t>https://pf.kakao.com/_nagUG/chat</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>613</v>
+        <v>206</v>
       </c>
       <c r="Q3" t="n">
-        <v>3994</v>
+        <v>1537</v>
       </c>
       <c r="R3" t="n">
-        <v>4607</v>
+        <v>1743</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1095182275</t>
+          <t>1362495075</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095182275</t>
+          <t>https://m.place.naver.com/place/1362495075</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오브디의원</t>
+          <t>비타민의원 분당점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dr_kkang@naver.com</t>
+          <t>vitaderm@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1383-5702</t>
+          <t>0507-1481-0298</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 젤존타워1 5층 510호 오브디의원</t>
+          <t>경기도 성남시 분당구 서현로210번길 2 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dr_kkang</t>
+          <t>http://www.vitaminclinic.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="Q4" t="n">
-        <v>2774</v>
+        <v>5428</v>
       </c>
       <c r="R4" t="n">
-        <v>3066</v>
+        <v>5740</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1260816786</t>
+          <t>13182156</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260816786</t>
+          <t>https://m.place.naver.com/place/13182156</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,44 +846,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오늘맑음의원 분당</t>
+          <t>미금동안마녀의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>familiar8622@naver.com</t>
+          <t>mintcavatina@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-709-7202</t>
+          <t>0507-1379-4725</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 2 5층 501호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 2층 206호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/clear_today1</t>
+          <t>http://www.witchclinic.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>535</v>
+        <v>494</v>
       </c>
       <c r="Q5" t="n">
-        <v>3941</v>
+        <v>248</v>
       </c>
       <c r="R5" t="n">
-        <v>4476</v>
+        <v>742</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1014948722</t>
+          <t>1301944577</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1014948722</t>
+          <t>https://m.place.naver.com/place/1301944577</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>밴스의원 판교역</t>
+          <t>진스킨의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lcevsly@naver.com</t>
+          <t>zinskin1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>031-8039-7570</t>
+          <t>0507-1446-1061</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠판교 3층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pangyo.vandsclinic.co.kr/?channel=4155</t>
+          <t>http://www.zinskin.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1868</v>
+        <v>435</v>
       </c>
       <c r="Q6" t="n">
-        <v>702</v>
+        <v>412</v>
       </c>
       <c r="R6" t="n">
-        <v>2570</v>
+        <v>847</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1947822332</t>
+          <t>33136407</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1947822332</t>
+          <t>https://m.place.naver.com/place/33136407</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>소호의원</t>
+          <t>삼성맑은피부과의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mbzoo91@naver.com</t>
+          <t>sspureclinic@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-702-5060</t>
+          <t>031-698-4016</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 30 소호클리닉</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://sohoclinic.co.kr</t>
+          <t>http://sspureclinic.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,22 +1082,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>330</v>
+        <v>453</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="R7" t="n">
-        <v>351</v>
+        <v>660</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1935241872</t>
+          <t>1582994500</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935241872</t>
+          <t>https://m.place.naver.com/place/1582994500</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,39 +1128,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>미소앤의원</t>
+          <t>소호의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>misoenclinic@naver.com</t>
+          <t>mbzoo91@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1495-7478</t>
+          <t>031-702-5060</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 168 미도프라자 6층 601호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 30 소호클리닉</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/misoenclinic</t>
+          <t>http://sohoclinic.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>156</v>
+        <v>330</v>
       </c>
       <c r="Q8" t="n">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="R8" t="n">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1467523840</t>
+          <t>1935241872</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467523840</t>
+          <t>https://m.place.naver.com/place/1935241872</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1222,44 +1222,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>블리비의원 분당점</t>
+          <t>힐하우스피부과의원 판교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sungjaelwwhyu@naver.com</t>
+          <t>healhousepg@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1833-3130</t>
+          <t>0507-1358-7438</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 2 성지하이츠텔 2층</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.velyb.kr/</t>
+          <t>https://www.healhousepg.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1270,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1341</v>
+        <v>293</v>
       </c>
       <c r="Q9" t="n">
-        <v>2544</v>
+        <v>311</v>
       </c>
       <c r="R9" t="n">
-        <v>3885</v>
+        <v>604</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2076023323</t>
+          <t>1245847654</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076023323</t>
+          <t>https://m.place.naver.com/place/1245847654</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1316,39 +1316,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>닥터스피부과의원 서판교</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>doctorspg@naver.com</t>
-        </is>
-      </c>
+          <t>리즈온의원 분당</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-698-3088</t>
+          <t>031-705-0870</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 237 2층</t>
+          <t>경기도 성남시 분당구 분당로53번길 11 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://seopangyo.doctors365.co.kr</t>
+          <t>https://bundang.lizonclinic.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1364,22 +1360,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>319</v>
+        <v>1086</v>
       </c>
       <c r="Q10" t="n">
-        <v>90</v>
+        <v>2648</v>
       </c>
       <c r="R10" t="n">
-        <v>409</v>
+        <v>3734</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1937925934</t>
+          <t>1231128843</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1937925934</t>
+          <t>https://m.place.naver.com/place/1231128843</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>다시봄날의원 분당</t>
+          <t>닥터스피부과의원 서판교</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yesokkim0510@naver.com</t>
+          <t>doctorspg@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1488-7676</t>
+          <t>031-698-3088</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 제5층 501-2호</t>
+          <t>경기도 성남시 분당구 운중로 237 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://bd.springdayclinic.com/</t>
+          <t>http://seopangyo.doctors365.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>932</v>
+        <v>319</v>
       </c>
       <c r="Q11" t="n">
-        <v>5248</v>
+        <v>92</v>
       </c>
       <c r="R11" t="n">
-        <v>6180</v>
+        <v>411</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1986908099</t>
+          <t>1937925934</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986908099</t>
+          <t>https://m.place.naver.com/place/1937925934</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1500,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>포레스트의원</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>forest_derma@naver.com</t>
-        </is>
-      </c>
+          <t>분당 맥스웰의원</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1343-3890</t>
+          <t>031-717-5824</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로335번길 5 N타운빌딩 4층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 7 301호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://forest.quv.kr</t>
+          <t>http://bundang.maxwellhair.com/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1552,7 +1544,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>593</v>
+        <v>96</v>
       </c>
       <c r="Q12" t="n">
-        <v>6306</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>6899</v>
+        <v>108</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>32430482</t>
+          <t>1494157050</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32430482</t>
+          <t>https://m.place.naver.com/place/1494157050</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1598,48 +1590,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>노블클래식의원 분당</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>miosol@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>team@madeinreal.com</t>
-        </is>
-      </c>
+          <t>데이뷰의원 분당점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>031-707-7930</t>
+          <t>0507-1395-8031</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 6 대덕프라자 407호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자3 2층 206호, 207호, 211호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.noblebundang.com/</t>
+          <t>https://www.daybeauclinic12.com</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1659,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>491</v>
+        <v>3110</v>
       </c>
       <c r="Q13" t="n">
-        <v>957</v>
+        <v>11316</v>
       </c>
       <c r="R13" t="n">
-        <v>1448</v>
+        <v>14426</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1674,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>35701207</t>
+          <t>1094772288</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35701207</t>
+          <t>https://m.place.naver.com/place/1094772288</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1696,29 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>이지함피부과의원 분당점</t>
+          <t>늘샤인의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bundangleejiham@naver.com</t>
+          <t>asclinic@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1440-2105</t>
+          <t>0507-1481-7894</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 204 엘지분당에클라트2차 402, 403호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 11 글라스타워 3층 늘샤인의원</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bundangleejiham</t>
+          <t>http://alwaysshineclinic.com</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1728,7 +1712,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1744,22 +1728,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>228</v>
+        <v>515</v>
       </c>
       <c r="Q14" t="n">
-        <v>383</v>
+        <v>3196</v>
       </c>
       <c r="R14" t="n">
-        <v>611</v>
+        <v>3711</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1768,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13234600</t>
+          <t>1606161160</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13234600</t>
+          <t>https://m.place.naver.com/place/1606161160</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1790,29 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>예라인의원 분당</t>
+          <t>샤인유의원 분당</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>planet46635@naver.com</t>
+          <t>madeu_bd@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>031-703-4400</t>
+          <t>031-698-2555</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 506호</t>
+          <t>경기도 성남시 분당구 황새울로312번길 5 세광빌딩 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/planet46635</t>
+          <t>https://blog.naver.com/madeu_bd</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1838,7 +1822,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1847,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>145</v>
+        <v>670</v>
       </c>
       <c r="Q15" t="n">
-        <v>6717</v>
+        <v>321</v>
       </c>
       <c r="R15" t="n">
-        <v>6862</v>
+        <v>991</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1862,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1343652932</t>
+          <t>1973024753</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1343652932</t>
+          <t>https://m.place.naver.com/place/1973024753</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1884,29 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>링클스탑의원 분당서현</t>
+          <t>루이의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wrinklestop@naver.com</t>
+          <t>louisclinic-4008@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1341-0516</t>
+          <t>0507-1398-4009</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 184 217호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_nagUG/chat</t>
+          <t>http://louisclinic.com/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1916,7 +1900,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1941,13 +1925,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>206</v>
+        <v>406</v>
       </c>
       <c r="Q16" t="n">
-        <v>1512</v>
+        <v>2432</v>
       </c>
       <c r="R16" t="n">
-        <v>1718</v>
+        <v>2838</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1956,17 +1940,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1362495075</t>
+          <t>36428162</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1362495075</t>
+          <t>https://m.place.naver.com/place/36428162</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1978,29 +1962,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>포에버의원 분당</t>
+          <t>유앤아이피부과의원 분당미금점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4everbun@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>wldnjs8802@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mdvision@nate.com</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1365-8348</t>
+          <t>031-8039-6021</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+          <t>경기도 성남시 분당구 돌마로 86 엘레강스프라자 2동 2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://bd.4-ever.co.kr</t>
+          <t>https://www.bmuni114.co.kr/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2015,7 +2003,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2035,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>982</v>
+        <v>1062</v>
       </c>
       <c r="Q17" t="n">
-        <v>2907</v>
+        <v>3051</v>
       </c>
       <c r="R17" t="n">
-        <v>3889</v>
+        <v>4113</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2050,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>20747205</t>
+          <t>2063670518</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20747205</t>
+          <t>https://m.place.naver.com/place/2063670518</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2072,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아비쥬의원 분당</t>
+          <t>분당예쁨주의쁨의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hj_4326@naver.com</t>
+          <t>olivia9532@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>031-607-1717</t>
+          <t>031-703-3010</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 10 동호프라자 401호</t>
+          <t>경기도 성남시 분당구 분당로53번길 12 서현 나산플라자 4층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hj_4326</t>
+          <t>http://www.ppeum10.com</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2129,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2129</v>
+        <v>871</v>
       </c>
       <c r="Q18" t="n">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="R18" t="n">
-        <v>2406</v>
+        <v>888</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2144,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1202847355</t>
+          <t>1028564181</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202847355</t>
+          <t>https://m.place.naver.com/place/1028564181</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2166,44 +2154,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>루이의원</t>
+          <t>분당 톡스앤필의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>louisclinic-4008@naver.com</t>
+          <t>toxnfill5@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1398-4009</t>
+          <t>031-707-3500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 3층</t>
+          <t>경기도 성남시 분당구 성남대로343번길 12-2 5층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://louisclinic.com/</t>
+          <t>https://www.toxnfill5.com</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2223,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>405</v>
+        <v>829</v>
       </c>
       <c r="Q19" t="n">
-        <v>2429</v>
+        <v>5756</v>
       </c>
       <c r="R19" t="n">
-        <v>2834</v>
+        <v>6585</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2238,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36428162</t>
+          <t>1299969468</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428162</t>
+          <t>https://m.place.naver.com/place/1299969468</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2260,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>미금동안마녀의원</t>
+          <t>아젤린의원 정자</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mintcavatina@naver.com</t>
+          <t>azelin-bundang@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1379-4725</t>
+          <t>0507-1383-1745</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 2층 206호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존타워3 3층 306호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.witchclinic.com/</t>
+          <t>http://www.azelin.co.kr/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2317,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>491</v>
+        <v>886</v>
       </c>
       <c r="Q20" t="n">
-        <v>245</v>
+        <v>817</v>
       </c>
       <c r="R20" t="n">
-        <v>736</v>
+        <v>1703</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2332,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1301944577</t>
+          <t>37745081</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1301944577</t>
+          <t>https://m.place.naver.com/place/37745081</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2354,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>티앤티의원</t>
+          <t>메이퓨어의원 야탑점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fatrasue@naver.com</t>
+          <t>minday123@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>031-608-0085</t>
+          <t>031-399-9990</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 12 5층</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 6층 608호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://tntclinic.kr/</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2386,12 +2374,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2411,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1465</v>
+        <v>2479</v>
       </c>
       <c r="Q21" t="n">
-        <v>3002</v>
+        <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>4467</v>
+        <v>2503</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2426,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1778414883</t>
+          <t>36654949</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1778414883</t>
+          <t>https://m.place.naver.com/place/36654949</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2448,44 +2436,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>뷰티라운지의원 판교점</t>
+          <t>리뉴미피부과의원 분당</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>beautyloungeclinic@naver.com</t>
+          <t>mdderma@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>031-698-3727</t>
+          <t>031-711-6711</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움타워 2동 지하1층 뷰티라운지의원</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-3 여민빌딩 4층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://pangyo.beautyloungeclinic.com/</t>
+          <t>https://blog.naver.com/mdderma</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2496,7 +2484,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2505,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>549</v>
+        <v>838</v>
       </c>
       <c r="Q22" t="n">
-        <v>2293</v>
+        <v>147</v>
       </c>
       <c r="R22" t="n">
-        <v>2842</v>
+        <v>985</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2520,17 +2508,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1742515435</t>
+          <t>36432617</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742515435</t>
+          <t>https://m.place.naver.com/place/36432617</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2542,24 +2530,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아이로피부과의원</t>
+          <t>바른피부과의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fogunion@naver.com</t>
+          <t>gp3465@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>031-8016-1675</t>
+          <t>0507-1407-5500</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 401호</t>
+          <t>경기도 성남시 분당구 판교로 435 동양프라자 305호 바른피부과의원</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2599,13 +2587,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>282</v>
+        <v>233</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2614,17 +2602,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>20343581</t>
+          <t>1045465077</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20343581</t>
+          <t>https://m.place.naver.com/place/1045465077</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2636,29 +2624,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아름다운나라피부과의원 분당</t>
+          <t>아이로피부과의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>anaderma@naver.com</t>
+          <t>fogunion@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>031-707-0878</t>
+          <t>031-8016-1675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 분당문화센터 6층</t>
+          <t>경기도 성남시 분당구 운중로 142 401호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anaderma</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2668,12 +2656,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2689,17 +2677,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>381</v>
+        <v>282</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2708,17 +2696,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13517048</t>
+          <t>20343581</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13517048</t>
+          <t>https://m.place.naver.com/place/20343581</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2730,39 +2718,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>벨리에의원</t>
+          <t>분당정자 셀린의원</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bundangsb@naver.com</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>cellinclinic-bundang@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>webtick@gmail.com</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1428-5859</t>
+          <t>031-1833-6372</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 340 5층</t>
+          <t>경기도 성남시 분당구 성남대로 349 301호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://bellierclinic.com</t>
+          <t>https://www.cellinclinic10.com/clinicInfoCellin/selfReserve.php</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2787,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>962</v>
+        <v>1016</v>
       </c>
       <c r="Q25" t="n">
-        <v>384</v>
+        <v>4948</v>
       </c>
       <c r="R25" t="n">
-        <v>1346</v>
+        <v>5964</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2802,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1362445992</t>
+          <t>1159993527</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1362445992</t>
+          <t>https://m.place.naver.com/place/1159993527</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2824,29 +2816,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스앤유피부과의원</t>
+          <t>메이린의원 판교</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abeer4u@naver.com</t>
+          <t>pangyomaylin@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>031-714-0808</t>
+          <t>0507-1301-3246</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로200번길 9-7 판테온 빌딩 2층 에스앤유피부과</t>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 10층 메이린클리닉 판교점</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/abeer4u</t>
+          <t>https://www.instagram.com/maylinclinic_pg/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2861,7 +2853,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2877,17 +2869,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="R26" t="n">
-        <v>181</v>
+        <v>265</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2896,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13186238</t>
+          <t>37035893</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13186238</t>
+          <t>https://m.place.naver.com/place/37035893</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2918,44 +2910,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>삼성맑은피부과의원</t>
+          <t>펄피부과의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sspureclinic@naver.com</t>
+          <t>o_o1793@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-698-4016</t>
+          <t>031-703-3733</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 4층</t>
+          <t>경기도 성남시 분당구 분당로 43 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://sspureclinic.com</t>
+          <t>https://blog.naver.com/o_o1793</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2971,17 +2963,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>453</v>
+        <v>340</v>
       </c>
       <c r="Q27" t="n">
-        <v>206</v>
+        <v>514</v>
       </c>
       <c r="R27" t="n">
-        <v>659</v>
+        <v>854</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2990,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1582994500</t>
+          <t>13454651</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1582994500</t>
+          <t>https://m.place.naver.com/place/13454651</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3012,33 +3004,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유앤아이피부과의원 분당미금점</t>
+          <t>포에버의원 분당</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wldnjs8802@naver.com</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+          <t>4everbun@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>031-8039-6021</t>
+          <t>0507-1365-8348</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 86 엘레강스프라자 2동 2층</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.bmuni114.co.kr/</t>
+          <t>https://bd.4-ever.co.kr</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3053,7 +3041,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3073,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1040</v>
+        <v>982</v>
       </c>
       <c r="Q28" t="n">
-        <v>2981</v>
+        <v>2970</v>
       </c>
       <c r="R28" t="n">
-        <v>4021</v>
+        <v>3952</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3088,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2063670518</t>
+          <t>20747205</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2063670518</t>
+          <t>https://m.place.naver.com/place/20747205</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3110,39 +3098,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>메이퓨어의원 야탑점</t>
+          <t>서울메이피부과의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>minday123@naver.com</t>
+          <t>3021307@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>031-399-9990</t>
+          <t>031-713-7766</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 6층 608호</t>
+          <t>경기도 성남시 분당구 미금로 44 국민프라자 3층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3158,22 +3146,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2466</v>
+        <v>291</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>2490</v>
+        <v>296</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3182,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>36654949</t>
+          <t>13118933</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36654949</t>
+          <t>https://m.place.naver.com/place/13118933</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3204,34 +3192,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>더에이치의원 분당</t>
+          <t>스킨영의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>macclinic7061@naver.com</t>
+          <t>yumin3115@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1357-7061</t>
+          <t>031-716-3337</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 4층</t>
+          <t>경기도 성남시 분당구 백현로101번길 17 초림프라자 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://thehclinic.ad-media.kr</t>
+          <t>https://blog.naver.com/yumin3115</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3261,13 +3249,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>176</v>
+        <v>953</v>
       </c>
       <c r="Q30" t="n">
-        <v>1274</v>
+        <v>1575</v>
       </c>
       <c r="R30" t="n">
-        <v>1450</v>
+        <v>2528</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3276,17 +3264,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1828034209</t>
+          <t>1461069782</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828034209</t>
+          <t>https://m.place.naver.com/place/1461069782</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3298,44 +3286,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비타민의원 분당점</t>
+          <t>분당동안의원</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>vitaderm@naver.com</t>
+          <t>pix1246@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1481-0298</t>
+          <t>031-708-0822</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 2 3층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 35 현대프라자 4층 407호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.vitaminclinic.kr</t>
+          <t>http://www.donganclinicbd.com/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3355,13 +3343,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>312</v>
+        <v>515</v>
       </c>
       <c r="Q31" t="n">
-        <v>5393</v>
+        <v>1689</v>
       </c>
       <c r="R31" t="n">
-        <v>5705</v>
+        <v>2204</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3370,17 +3358,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13182156</t>
+          <t>12943172</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13182156</t>
+          <t>https://m.place.naver.com/place/12943172</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3392,48 +3380,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>유앤아이피부과의원 판교점</t>
+          <t>리버스의원 분당</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jccbtfu_411@naver.com</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+          <t>ups126@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>031-8016-6020</t>
+          <t>0507-1377-7086</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 12 판교미래에셋센터 2층 202, 203호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 19 2층 201, 202호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.pguni114.co.kr/</t>
+          <t>https://bd.reverseclinic.com/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3453,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1049</v>
+        <v>1031</v>
       </c>
       <c r="Q32" t="n">
-        <v>1621</v>
+        <v>954</v>
       </c>
       <c r="R32" t="n">
-        <v>2670</v>
+        <v>1985</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3468,17 +3452,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>19759020</t>
+          <t>2099954204</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19759020</t>
+          <t>https://m.place.naver.com/place/2099954204</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3490,39 +3474,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>톤즈의원 분당</t>
+          <t>파인트리피부과의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tones_bundang@naver.com</t>
+          <t>pinetree_derma_@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1489-5804</t>
+          <t>0507-1373-2095</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 225호</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 5층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://tonesclinic.co.kr/bundang</t>
+          <t>https://blog.naver.com/pinetree_derma_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3538,7 +3522,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3547,13 +3531,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2479</v>
+        <v>289</v>
       </c>
       <c r="Q33" t="n">
-        <v>7507</v>
+        <v>319</v>
       </c>
       <c r="R33" t="n">
-        <v>9986</v>
+        <v>608</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3562,17 +3546,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1049120141</t>
+          <t>1319261524</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049120141</t>
+          <t>https://m.place.naver.com/place/1319261524</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3584,29 +3568,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>분당동안의원</t>
+          <t>밴스의원 판교역</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>pix1246@naver.com</t>
+          <t>lcevsly@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>031-708-0822</t>
+          <t>031-8039-7570</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 35 현대프라자 4층 407호</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠판교 3층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.donganclinicbd.com/</t>
+          <t>https://pangyo.vandsclinic.co.kr/?channel=4155</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3621,7 +3605,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3637,17 +3621,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>512</v>
+        <v>1875</v>
       </c>
       <c r="Q34" t="n">
-        <v>1648</v>
+        <v>760</v>
       </c>
       <c r="R34" t="n">
-        <v>2160</v>
+        <v>2635</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3656,17 +3640,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>12943172</t>
+          <t>1947822332</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12943172</t>
+          <t>https://m.place.naver.com/place/1947822332</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3678,29 +3662,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>유어라인의원</t>
+          <t>유앤아이피부과의원 판교점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>yourlineclinic@naver.com</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>jccbtfu_411@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>mdvision@nate.com</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>031-715-3657</t>
+          <t>031-8016-6020</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 73 우방코아 5층 503호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 12 판교미래에셋센터 2층 202, 203호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xfxexdxhn</t>
+          <t>https://www.pguni114.co.kr/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3710,7 +3698,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3735,13 +3723,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>201</v>
+        <v>1050</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>1660</v>
       </c>
       <c r="R35" t="n">
-        <v>233</v>
+        <v>2710</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3750,17 +3738,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1898979899</t>
+          <t>19759020</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1898979899</t>
+          <t>https://m.place.naver.com/place/19759020</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3772,39 +3760,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>메이저피부과의원 분당점</t>
+          <t>티앤티의원</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bonpibu@naver.com</t>
+          <t>fatrasue@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1389-7345</t>
+          <t>031-608-0085</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로351번길 10 여암빌딩 3층</t>
+          <t>경기도 성남시 분당구 분당로53번길 12 5층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bonpibu</t>
+          <t>http://tntclinic.kr/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3820,22 +3808,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>225</v>
+        <v>1471</v>
       </c>
       <c r="Q36" t="n">
-        <v>201</v>
+        <v>2977</v>
       </c>
       <c r="R36" t="n">
-        <v>426</v>
+        <v>4448</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3844,17 +3832,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>19782204</t>
+          <t>1778414883</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19782204</t>
+          <t>https://m.place.naver.com/place/1778414883</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3866,39 +3854,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>파인트리피부과의원</t>
+          <t>다시봄날의원 분당</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pinetree_derma_@naver.com</t>
+          <t>yesokkim0510@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1373-2095</t>
+          <t>0507-1488-7676</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 5층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 제5층 501-2호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pinetree_derma_</t>
+          <t>https://bd.springdayclinic.com/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3914,7 +3902,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3923,13 +3911,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>285</v>
+        <v>936</v>
       </c>
       <c r="Q37" t="n">
-        <v>319</v>
+        <v>5366</v>
       </c>
       <c r="R37" t="n">
-        <v>604</v>
+        <v>6302</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3938,17 +3926,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1319261524</t>
+          <t>1986908099</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319261524</t>
+          <t>https://m.place.naver.com/place/1986908099</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3960,44 +3948,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>휴먼피부과의원 분당점</t>
+          <t>파랑새피부과의원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dermr@naver.com</t>
+          <t>bluebirdskin@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>031-713-9995</t>
+          <t>0507-1319-4171</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 97 다운타운 304호</t>
+          <t>경기도 성남시 분당구 수내로 39 2층 236호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://humanbd.co.kr/</t>
+          <t>https://blog.naver.com/bluebirdskin</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4008,7 +3996,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4017,13 +4005,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="Q38" t="n">
-        <v>259</v>
+        <v>336</v>
       </c>
       <c r="R38" t="n">
-        <v>434</v>
+        <v>617</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4032,17 +4020,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1452441194</t>
+          <t>1340499564</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452441194</t>
+          <t>https://m.place.naver.com/place/1340499564</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4054,44 +4042,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>파랑새피부과의원</t>
+          <t>휴먼피부과의원 분당점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bluebirdskin@naver.com</t>
+          <t>dermr@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1319-4171</t>
+          <t>031-713-9995</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 39 2층 236호</t>
+          <t>경기도 성남시 분당구 백현로 97 다운타운 304호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bluebirdskin</t>
+          <t>https://humanbd.co.kr/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4102,7 +4090,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4111,13 +4099,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>281</v>
+        <v>174</v>
       </c>
       <c r="Q39" t="n">
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="R39" t="n">
-        <v>617</v>
+        <v>433</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4126,17 +4114,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1340499564</t>
+          <t>1452441194</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340499564</t>
+          <t>https://m.place.naver.com/place/1452441194</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4148,34 +4136,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>메디큐브의원 분당서현</t>
+          <t>유어라인의원</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>yaguchenjae@naver.com</t>
+          <t>yourlineclinic@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1325-6277</t>
+          <t>031-715-3657</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 326 분당서현빌딩 별관 4층</t>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 5층 503호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.medicubesignature.com</t>
+          <t>http://pf.kakao.com/_xfxexdxhn</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4196,7 +4184,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4205,13 +4193,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2429</v>
+        <v>208</v>
       </c>
       <c r="Q40" t="n">
-        <v>800</v>
+        <v>34</v>
       </c>
       <c r="R40" t="n">
-        <v>3229</v>
+        <v>242</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4220,17 +4208,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1907560612</t>
+          <t>1898979899</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907560612</t>
+          <t>https://m.place.naver.com/place/1898979899</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4242,34 +4230,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>늘샤인의원</t>
+          <t>야탑밴스의원</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>asclinic@naver.com</t>
+          <t>y_yse0@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1481-7894</t>
+          <t>031-778-8828</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 11 글라스타워 3층 늘샤인의원</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 604호, 605호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://alwaysshineclinic.com</t>
+          <t>https://yatap.vandsclinic.co.kr/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4279,7 +4267,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4295,17 +4283,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>516</v>
+        <v>1154</v>
       </c>
       <c r="Q41" t="n">
-        <v>3194</v>
+        <v>4616</v>
       </c>
       <c r="R41" t="n">
-        <v>3710</v>
+        <v>5770</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4314,17 +4302,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1606161160</t>
+          <t>1733838797</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1606161160</t>
+          <t>https://m.place.naver.com/place/1733838797</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4336,29 +4324,33 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>연세모네피부과의원</t>
+          <t>리더스피부과의원 판교</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ghjk316@naver.com</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>leaderspgd@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>master@beautyleader.co.kr</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>031-709-6354</t>
+          <t>031-8023-5085</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 22 블루홀플라자</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 판교리더스피부과</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://leaders-pg.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4373,7 +4365,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4384,22 +4376,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>224</v>
+        <v>421</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>1469</v>
       </c>
       <c r="R42" t="n">
-        <v>234</v>
+        <v>1890</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4408,17 +4400,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>11538782</t>
+          <t>21697693</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11538782</t>
+          <t>https://m.place.naver.com/place/21697693</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4487,13 +4479,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="Q43" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="R43" t="n">
-        <v>1471</v>
+        <v>1492</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4512,7 +4504,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4524,29 +4516,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>리셋의원 분당</t>
+          <t>톤즈의원 분당</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>resetclinic_official@naver.com</t>
+          <t>tones_bundang@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1362-6644</t>
+          <t>0507-1489-5804</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 21 5층</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 225호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbsWQj</t>
+          <t>https://tonesclinic.co.kr/bundang</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4556,12 +4548,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4581,13 +4573,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>977</v>
+        <v>2505</v>
       </c>
       <c r="Q44" t="n">
-        <v>4905</v>
+        <v>7698</v>
       </c>
       <c r="R44" t="n">
-        <v>5882</v>
+        <v>10203</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4596,17 +4588,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1708856210</t>
+          <t>1049120141</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708856210</t>
+          <t>https://m.place.naver.com/place/1049120141</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4618,34 +4610,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>로즈피부과 분당점</t>
+          <t>오라클피부과의원 분당서현점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>roseclinic_@naver.com</t>
+          <t>oraclebd02@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1437-9970</t>
+          <t>031-707-4975</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 27 하나프라자 6층</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 서현프라자6층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://www.roseclinic.kr/</t>
+          <t>https://blog.naver.com/oraclebd02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4671,17 +4663,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>130</v>
+        <v>894</v>
       </c>
       <c r="Q45" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="R45" t="n">
-        <v>420</v>
+        <v>1189</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4690,17 +4682,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>12952311</t>
+          <t>11725308</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12952311</t>
+          <t>https://m.place.naver.com/place/11725308</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4712,34 +4704,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>리뉴미피부과의원 분당</t>
+          <t>로즈피부과 분당점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mdderma@naver.com</t>
+          <t>roseclinic_@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>031-711-6711</t>
+          <t>0507-1437-9970</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-3 여민빌딩 4층</t>
+          <t>경기도 성남시 분당구 느티로 27 하나프라자 6층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mdderma</t>
+          <t>http://www.roseclinic.kr/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4769,13 +4761,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>833</v>
+        <v>131</v>
       </c>
       <c r="Q46" t="n">
-        <v>148</v>
+        <v>291</v>
       </c>
       <c r="R46" t="n">
-        <v>981</v>
+        <v>422</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4784,17 +4776,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>36432617</t>
+          <t>12952311</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36432617</t>
+          <t>https://m.place.naver.com/place/12952311</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4806,34 +4798,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>아젤린의원 정자</t>
+          <t>이봉구피부과의원</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>azelin-bundang@naver.com</t>
+          <t>demiann-@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1383-1745</t>
+          <t>031-711-1213</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존타워3 3층 306호</t>
+          <t>경기도 성남시 분당구 내정로 170 동신파크빌딩 304호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.azelin.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4843,7 +4835,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4854,22 +4846,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>865</v>
+        <v>649</v>
       </c>
       <c r="Q47" t="n">
-        <v>817</v>
+        <v>31</v>
       </c>
       <c r="R47" t="n">
-        <v>1682</v>
+        <v>680</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4878,17 +4870,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>37745081</t>
+          <t>13036099</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37745081</t>
+          <t>https://m.place.naver.com/place/13036099</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4900,34 +4892,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>이봉구피부과의원</t>
+          <t>베네핏의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>demiann-@naver.com</t>
+          <t>benefitclinic-@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>031-711-1213</t>
+          <t>031-778-8253</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로 170 동신파크빌딩 304호</t>
+          <t>경기도 성남시 분당구 성남대로 151 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://benefitclinic.co.kr</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4937,7 +4929,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4948,22 +4940,22 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>648</v>
+        <v>333</v>
       </c>
       <c r="Q48" t="n">
-        <v>31</v>
+        <v>2987</v>
       </c>
       <c r="R48" t="n">
-        <v>679</v>
+        <v>3320</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4972,17 +4964,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13036099</t>
+          <t>1034660593</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13036099</t>
+          <t>https://m.place.naver.com/place/1034660593</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4994,34 +4986,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>미금메이퓨어의원</t>
+          <t>메디큐브의원 분당서현</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>buggmi33@naver.com</t>
+          <t>yaguchenjae@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>031-715-9960</t>
+          <t>0507-1325-6277</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층</t>
+          <t>경기도 성남시 분당구 황새울로 326 분당서현빌딩 별관 4층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/community/migeum</t>
+          <t>http://www.medicubesignature.com</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5051,13 +5043,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2505</v>
+        <v>2428</v>
       </c>
       <c r="Q49" t="n">
-        <v>2151</v>
+        <v>803</v>
       </c>
       <c r="R49" t="n">
-        <v>4656</v>
+        <v>3231</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5066,17 +5058,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>593028781</t>
+          <t>1907560612</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/593028781</t>
+          <t>https://m.place.naver.com/place/1907560612</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5088,44 +5080,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>진스킨의원</t>
+          <t>벨리에의원</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>zinskin1@naver.com</t>
+          <t>ktlee79@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1446-1061</t>
+          <t>0507-1428-5859</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 6층</t>
+          <t>경기도 성남시 분당구 황새울로 340 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://www.zinskin.com/</t>
+          <t>http://bellierclinic.com</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5145,13 +5137,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>422</v>
+        <v>963</v>
       </c>
       <c r="Q50" t="n">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="R50" t="n">
-        <v>831</v>
+        <v>1347</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5160,17 +5152,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>33136407</t>
+          <t>1362445992</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33136407</t>
+          <t>https://m.place.naver.com/place/1362445992</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5243,13 +5235,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Q51" t="n">
-        <v>3004</v>
+        <v>3105</v>
       </c>
       <c r="R51" t="n">
-        <v>3610</v>
+        <v>3710</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5268,7 +5260,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5280,34 +5272,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>바른피부과의원</t>
+          <t>뷰티라운지의원 판교점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gp3465@naver.com</t>
+          <t>beautyloungeclinic@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1407-5500</t>
+          <t>031-698-3727</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 435 동양프라자 305호 바른피부과의원</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움타워 2동 지하1층 뷰티라운지의원</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pangyo.beautyloungeclinic.com/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5328,22 +5320,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>229</v>
+        <v>552</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>2294</v>
       </c>
       <c r="R52" t="n">
-        <v>233</v>
+        <v>2846</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5352,17 +5344,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1045465077</t>
+          <t>1742515435</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045465077</t>
+          <t>https://m.place.naver.com/place/1742515435</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5374,39 +5366,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>서울예미인피부과의원</t>
+          <t>아비쥬의원 분당</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>atidarch@naver.com</t>
+          <t>hj_4326@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>031-711-0280</t>
+          <t>031-607-1717</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 BYC건물 2층</t>
+          <t>경기도 성남시 분당구 분당로53번길 10 동호프라자 401호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://yemein.com/</t>
+          <t>https://blog.naver.com/hj_4326</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5427,17 +5419,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>563</v>
+        <v>2126</v>
       </c>
       <c r="Q53" t="n">
-        <v>225</v>
+        <v>292</v>
       </c>
       <c r="R53" t="n">
-        <v>788</v>
+        <v>2418</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5446,17 +5438,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13032291</t>
+          <t>1202847355</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13032291</t>
+          <t>https://m.place.naver.com/place/1202847355</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5468,29 +5460,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>스킨영의원</t>
+          <t>분당우태하피부과의원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>yumin3115@naver.com</t>
+          <t>wwskinw@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>031-716-3337</t>
+          <t>031-781-1676</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 17 초림프라자 2층</t>
+          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 5층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yumin3115</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5500,12 +5492,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5516,22 +5508,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>951</v>
+        <v>9</v>
       </c>
       <c r="Q54" t="n">
-        <v>1538</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2489</v>
+        <v>9</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5540,17 +5532,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1461069782</t>
+          <t>2087764851</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461069782</t>
+          <t>https://m.place.naver.com/place/2087764851</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5562,39 +5554,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>샤인유의원 분당</t>
+          <t>심덕택피부과의원</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>madeu_bd@naver.com</t>
+          <t>0x0030@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>031-698-2555</t>
+          <t>031-716-1353</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로312번길 5 세광빌딩 3층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 306호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madeu_bd</t>
+          <t>http://www.goldskin.co.kr/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5615,17 +5607,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>674</v>
+        <v>1249</v>
       </c>
       <c r="Q55" t="n">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="R55" t="n">
-        <v>995</v>
+        <v>1264</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5634,17 +5626,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1973024753</t>
+          <t>11719317</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973024753</t>
+          <t>https://m.place.naver.com/place/11719317</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5656,34 +5648,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>분당판교 아르버의원</t>
+          <t>오브디의원</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>chocosoyeon@naver.com</t>
+          <t>dr_kkang@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1386-3591</t>
+          <t>0507-1383-5702</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로 84 2층 202호</t>
+          <t>경기도 성남시 분당구 느티로 16 젤존타워1 5층 510호 오브디의원</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://arborclinic.kr</t>
+          <t>https://blog.naver.com/dr_kkang</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5713,13 +5705,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>170</v>
+        <v>293</v>
       </c>
       <c r="Q56" t="n">
-        <v>162</v>
+        <v>2826</v>
       </c>
       <c r="R56" t="n">
-        <v>332</v>
+        <v>3119</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5728,17 +5720,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2010135298</t>
+          <t>1260816786</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010135298</t>
+          <t>https://m.place.naver.com/place/1260816786</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5750,29 +5742,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>판교연세피부과의원</t>
+          <t>아름다운나라피부과의원 분당</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>thewisepine@naver.com</t>
+          <t>anaderma@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>031-8017-5252</t>
+          <t>031-707-0878</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 자유퍼스트프라자 1동 301호</t>
+          <t>경기도 성남시 분당구 황새울로 332 분당문화센터 6층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/anaderma</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5782,12 +5774,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5803,17 +5795,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>250</v>
+        <v>373</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R57" t="n">
-        <v>262</v>
+        <v>381</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5822,17 +5814,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>21423768</t>
+          <t>13517048</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21423768</t>
+          <t>https://m.place.naver.com/place/13517048</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5844,29 +5836,33 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>베네핏의원</t>
+          <t>노블클래식의원 분당</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>benefitclinic-@naver.com</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>miosol@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>team@madeinreal.com</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>031-778-8253</t>
+          <t>031-707-7930</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 2층</t>
+          <t>경기도 성남시 분당구 성남대로926번길 6 대덕프라자 407호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://benefitclinic.co.kr</t>
+          <t>https://www.noblebundang.com/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5876,7 +5872,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5901,13 +5897,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>333</v>
+        <v>493</v>
       </c>
       <c r="Q58" t="n">
-        <v>2937</v>
+        <v>957</v>
       </c>
       <c r="R58" t="n">
-        <v>3270</v>
+        <v>1450</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5916,17 +5912,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1034660593</t>
+          <t>35701207</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034660593</t>
+          <t>https://m.place.naver.com/place/35701207</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5938,39 +5934,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>오월의아침피부과의원</t>
+          <t>메이저피부과의원 분당점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>maymorning_05@naver.com</t>
+          <t>bonpibu@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>031-717-5207</t>
+          <t>0507-1389-7345</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 46 광천프라자 5층 오월의아침피부과의원</t>
+          <t>경기도 성남시 분당구 황새울로351번길 10 여암빌딩 3층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.maymorning.kr/</t>
+          <t>https://blog.naver.com/bonpibu</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5986,22 +5982,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>501</v>
+        <v>225</v>
       </c>
       <c r="Q59" t="n">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="R59" t="n">
-        <v>609</v>
+        <v>429</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6010,17 +6006,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>12771235</t>
+          <t>19782204</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12771235</t>
+          <t>https://m.place.naver.com/place/19782204</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6032,29 +6028,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>차앤박피부과의원 분당서현점</t>
+          <t>오월의아침피부과의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cnpsh7229@naver.com</t>
+          <t>maymorning_05@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>031-709-7229</t>
+          <t>031-717-5207</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 9 정현빌딩 8층</t>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 5층 오월의아침피부과의원</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.cnpskin.co.kr/hos/main.php?groupid=cnpskin09</t>
+          <t>http://www.maymorning.kr/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6064,7 +6060,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6089,13 +6085,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>348</v>
+        <v>501</v>
       </c>
       <c r="Q60" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="R60" t="n">
-        <v>402</v>
+        <v>606</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6104,17 +6100,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>11696898</t>
+          <t>12771235</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11696898</t>
+          <t>https://m.place.naver.com/place/12771235</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6126,39 +6122,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>오라클피부과의원 분당서현점</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>oraclebd02@naver.com</t>
-        </is>
-      </c>
+          <t>서울예미인피부과의원</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>031-707-4975</t>
+          <t>031-711-0280</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 서현프라자6층</t>
+          <t>경기도 성남시 분당구 성남대로 912 BYC건물 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oraclebd02</t>
+          <t>http://yemein.com/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6183,13 +6175,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>893</v>
+        <v>563</v>
       </c>
       <c r="Q61" t="n">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="R61" t="n">
-        <v>1188</v>
+        <v>790</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6198,17 +6190,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>11725308</t>
+          <t>13032291</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11725308</t>
+          <t>https://m.place.naver.com/place/13032291</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6220,33 +6212,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>분당정자 셀린의원</t>
+          <t>분당프리미어의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>cellinclinic-bundang@naver.com</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>webtick@gmail.com</t>
-        </is>
-      </c>
+          <t>isigary@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>031-1833-6372</t>
+          <t>0507-1405-7918</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 349 301호</t>
+          <t>경기도 성남시 분당구 백현로101번길 29 2층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.cellinclinic10.com/clinicInfoCellin/selfReserve.php</t>
+          <t>https://blog.naver.com/isigary</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6256,12 +6244,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6272,7 +6260,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6281,13 +6269,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1015</v>
+        <v>620</v>
       </c>
       <c r="Q62" t="n">
-        <v>4894</v>
+        <v>3994</v>
       </c>
       <c r="R62" t="n">
-        <v>5909</v>
+        <v>4614</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6296,17 +6284,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1159993527</t>
+          <t>1095182275</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159993527</t>
+          <t>https://m.place.naver.com/place/1095182275</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6318,29 +6306,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>미앤미의원 분당</t>
+          <t>예라인의원 분당</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>asubtend@naver.com</t>
+          <t>planet46635@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>031-704-1171</t>
+          <t>031-703-4400</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 분당서현신영팰리스타워 4층</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 506호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/asubtend</t>
+          <t>https://blog.naver.com/planet46635</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6366,7 +6354,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6375,13 +6363,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>742</v>
+        <v>148</v>
       </c>
       <c r="Q63" t="n">
-        <v>5401</v>
+        <v>6785</v>
       </c>
       <c r="R63" t="n">
-        <v>6143</v>
+        <v>6933</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6390,17 +6378,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>37341394</t>
+          <t>1343652932</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37341394</t>
+          <t>https://m.place.naver.com/place/1343652932</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6412,34 +6400,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>분당예쁨주의쁨의원</t>
+          <t>차앤박피부과의원 분당서현점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jlles1@naver.com</t>
+          <t>cnpsh7229@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>031-703-3010</t>
+          <t>031-709-7229</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 12 서현 나산플라자 4층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 9 정현빌딩 8층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.ppeum10.com</t>
+          <t>http://www.cnpskin.co.kr/hos/main.php?groupid=cnpskin09</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6449,7 +6437,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6460,7 +6448,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6469,13 +6457,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>869</v>
+        <v>348</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="R64" t="n">
-        <v>886</v>
+        <v>402</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6484,17 +6472,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1028564181</t>
+          <t>11696898</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028564181</t>
+          <t>https://m.place.naver.com/place/11696898</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6506,44 +6494,44 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>리즈온의원 분당</t>
+          <t>분당닥터에버스의원</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>daru0527@naver.com</t>
+          <t>77bundang@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>031-705-0870</t>
+          <t>0507-1389-7537</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 11 4층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 35 서현현대프라자 3층 304호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://bundang.lizonclinic.co.kr</t>
+          <t>https://www.evers29.co.kr/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6554,22 +6542,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1071</v>
+        <v>175</v>
       </c>
       <c r="Q65" t="n">
-        <v>2616</v>
+        <v>444</v>
       </c>
       <c r="R65" t="n">
-        <v>3687</v>
+        <v>619</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6578,17 +6566,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1231128843</t>
+          <t>1100909582</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231128843</t>
+          <t>https://m.place.naver.com/place/1100909582</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6600,34 +6588,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>데이뷰의원 분당점</t>
+          <t>포레스트의원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nextday92@naver.com</t>
+          <t>forest_derma@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1395-8031</t>
+          <t>0507-1343-3890</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자3 2층 206호, 207호, 211호</t>
+          <t>경기도 성남시 분당구 황새울로335번길 5 N타운빌딩 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.daybeauclinic12.com</t>
+          <t>https://forest.quv.kr</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6637,7 +6625,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6657,13 +6645,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3057</v>
+        <v>596</v>
       </c>
       <c r="Q66" t="n">
-        <v>11075</v>
+        <v>6346</v>
       </c>
       <c r="R66" t="n">
-        <v>14132</v>
+        <v>6942</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6672,17 +6660,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1094772288</t>
+          <t>32430482</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094772288</t>
+          <t>https://m.place.naver.com/place/32430482</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6694,29 +6682,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>리버스의원 분당</t>
+          <t>블리비의원 분당점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>cap0153@naver.com</t>
+          <t>lukxymxl@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1377-7086</t>
+          <t>1833-3130</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 19 2층 201, 202호</t>
+          <t>경기도 성남시 분당구 서현로210번길 2 성지하이츠텔 2층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://bd.reverseclinic.com/</t>
+          <t>https://www.velyb.kr/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6731,7 +6719,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6742,22 +6730,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1031</v>
+        <v>1343</v>
       </c>
       <c r="Q67" t="n">
-        <v>832</v>
+        <v>2573</v>
       </c>
       <c r="R67" t="n">
-        <v>1863</v>
+        <v>3916</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6766,17 +6754,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2099954204</t>
+          <t>2076023323</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099954204</t>
+          <t>https://m.place.naver.com/place/2076023323</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6788,33 +6776,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>리더스피부과의원 판교</t>
+          <t>오늘맑음의원 분당</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>leaderspgd@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>master@beautyleader.co.kr</t>
-        </is>
-      </c>
+          <t>familiar8622@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>031-8023-5085</t>
+          <t>031-709-7202</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 판교리더스피부과</t>
+          <t>경기도 성남시 분당구 서현로210번길 2 5층 501호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://leaders-pg.com/</t>
+          <t>https://www.instagram.com/clear_today1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6824,12 +6808,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6849,13 +6833,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>421</v>
+        <v>535</v>
       </c>
       <c r="Q68" t="n">
-        <v>1426</v>
+        <v>3930</v>
       </c>
       <c r="R68" t="n">
-        <v>1847</v>
+        <v>4465</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6864,17 +6848,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>21697693</t>
+          <t>1014948722</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21697693</t>
+          <t>https://m.place.naver.com/place/1014948722</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6886,34 +6870,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>수내메이퓨어의원</t>
+          <t>미앤미의원 분당</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8832707@naver.com</t>
+          <t>asubtend@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>031-717-3336</t>
+          <t>031-704-1171</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 97 수내동 다운타운 1004호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 분당서현신영팰리스타워 4층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>https://blog.naver.com/asubtend</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6923,7 +6907,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6934,22 +6918,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1063</v>
+        <v>756</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>5466</v>
       </c>
       <c r="R69" t="n">
-        <v>1097</v>
+        <v>6222</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6958,17 +6942,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1638817358</t>
+          <t>37341394</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1638817358</t>
+          <t>https://m.place.naver.com/place/37341394</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6980,29 +6964,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>분당 맥스웰의원</t>
+          <t>미금메이퓨어의원</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hazy_920726@naver.com</t>
+          <t>buggmi33@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>031-717-5824</t>
+          <t>031-715-9960</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 7 301호</t>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://bundang.maxwellhair.com/</t>
+          <t>https://www.maypureclinic.com/community/migeum</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7012,7 +6996,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7037,13 +7021,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>96</v>
+        <v>2529</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>2184</v>
       </c>
       <c r="R70" t="n">
-        <v>108</v>
+        <v>4713</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7052,17 +7036,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1494157050</t>
+          <t>593028781</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494157050</t>
+          <t>https://m.place.naver.com/place/593028781</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7074,29 +7058,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>심덕택피부과의원</t>
+          <t>수내메이퓨어의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0x0030@naver.com</t>
+          <t>8832707@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>031-716-1353</t>
+          <t>031-717-3336</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 306호</t>
+          <t>경기도 성남시 분당구 백현로 97 수내동 다운타운 1004호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://www.goldskin.co.kr/</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7106,12 +7090,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7122,7 +7106,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7131,13 +7115,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1247</v>
+        <v>1072</v>
       </c>
       <c r="Q71" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="R71" t="n">
-        <v>1262</v>
+        <v>1106</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7146,17 +7130,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>11719317</t>
+          <t>1638817358</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11719317</t>
+          <t>https://m.place.naver.com/place/1638817358</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7168,44 +7152,44 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>야탑밴스의원</t>
+          <t>미소앤의원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>y_yse0@naver.com</t>
+          <t>misoenclinic@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>031-778-8828</t>
+          <t>0507-1495-7478</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 604호, 605호</t>
+          <t>경기도 성남시 분당구 성남대로 168 미도프라자 6층 601호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://yatap.vandsclinic.co.kr/</t>
+          <t>https://blog.naver.com/misoenclinic</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7216,7 +7200,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7225,13 +7209,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1144</v>
+        <v>156</v>
       </c>
       <c r="Q72" t="n">
-        <v>4550</v>
+        <v>138</v>
       </c>
       <c r="R72" t="n">
-        <v>5694</v>
+        <v>294</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7240,17 +7224,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1733838797</t>
+          <t>1467523840</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1733838797</t>
+          <t>https://m.place.naver.com/place/1467523840</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7262,39 +7246,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>분당닥터에버스의원</t>
+          <t>이지함피부과의원 분당점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>77bundang@naver.com</t>
+          <t>bundangleejiham@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1389-7537</t>
+          <t>0507-1440-2105</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 35 서현현대프라자 3층 304호</t>
+          <t>경기도 성남시 분당구 서현로 204 엘지분당에클라트2차 402, 403호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.evers29.co.kr/</t>
+          <t>https://blog.naver.com/bundangleejiham</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7310,22 +7294,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="Q73" t="n">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="R73" t="n">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7334,17 +7318,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1100909582</t>
+          <t>13234600</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100909582</t>
+          <t>https://m.place.naver.com/place/13234600</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7356,34 +7340,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>힐하우스피부과의원 판교점</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>healhousepg@naver.com</t>
-        </is>
-      </c>
+          <t>연세모네피부과의원</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1358-7438</t>
+          <t>031-709-6354</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 131 2층</t>
+          <t>경기도 성남시 분당구 분당로53번길 22 블루홀플라자</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.healhousepg.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7393,7 +7373,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7404,22 +7384,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="Q74" t="n">
-        <v>307</v>
+        <v>10</v>
       </c>
       <c r="R74" t="n">
-        <v>599</v>
+        <v>234</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7428,17 +7408,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1245847654</t>
+          <t>11538782</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245847654</t>
+          <t>https://m.place.naver.com/place/11538782</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7450,34 +7430,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>분당 톡스앤필의원</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>toxnfill5@naver.com</t>
-        </is>
-      </c>
+          <t>플러스미피부과의원</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>031-707-3500</t>
+          <t>031-698-3300</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로343번길 12-2 5층</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리빌딩 3층 306호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.toxnfill5.com</t>
+          <t>http://www.pmskin.co.kr/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7487,7 +7463,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7498,22 +7474,22 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>826</v>
+        <v>175</v>
       </c>
       <c r="Q75" t="n">
-        <v>5719</v>
+        <v>351</v>
       </c>
       <c r="R75" t="n">
-        <v>6545</v>
+        <v>526</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7522,17 +7498,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1299969468</t>
+          <t>35452155</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299969468</t>
+          <t>https://m.place.naver.com/place/35452155</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7544,34 +7520,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>메이린의원 판교</t>
+          <t>리셋의원 분당</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>pangyomaylin@naver.com</t>
+          <t>resetclinic_official@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1301-3246</t>
+          <t>0507-1362-6644</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 10층 메이린클리닉 판교점</t>
+          <t>경기도 성남시 분당구 황새울로342번길 21 5층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maylinclinic_pg/</t>
+          <t>http://pf.kakao.com/_xbsWQj</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7592,7 +7568,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7601,13 +7577,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>118</v>
+        <v>982</v>
       </c>
       <c r="Q76" t="n">
-        <v>147</v>
+        <v>4971</v>
       </c>
       <c r="R76" t="n">
-        <v>265</v>
+        <v>5953</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7616,17 +7592,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>37035893</t>
+          <t>1708856210</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37035893</t>
+          <t>https://m.place.naver.com/place/1708856210</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
